--- a/processed/AI_Features_Data_Enriched.xlsx
+++ b/processed/AI_Features_Data_Enriched.xlsx
@@ -9,7 +9,6 @@
   <sheets>
     <sheet name="AI Features &amp; Agents" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Pricing Premium" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Initial Setup" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -9240,10 +9239,10 @@
     <col width="24" customWidth="1" min="8" max="8"/>
     <col width="24" customWidth="1" min="9" max="9"/>
     <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
-    <col width="24" customWidth="1" min="12" max="12"/>
-    <col width="60" customWidth="1" min="13" max="13"/>
-    <col width="60" customWidth="1" min="14" max="14"/>
+    <col width="60" customWidth="1" min="11" max="11"/>
+    <col width="60" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9299,22 +9298,22 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>Detail Page</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Pricing Details</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>AI Type</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Package</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Detail Page</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Pricing Details</t>
         </is>
       </c>
     </row>
@@ -9401,18 +9400,18 @@
       <c r="H3" s="2" t="inlineStr"/>
       <c r="I3" s="2" t="inlineStr"/>
       <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="2" t="inlineStr"/>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>https://discovery-center.cloud.sap/ai-feature/988b6b7c-ac4f-4c5f-be46-0366c7dc5a2e/</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t>AI Units requeridos. En Pricing Details se indica activación mediante “Activate with AI Units”; precio disponible bajo solicitud; duración contractual disponible bajo solicitud; tiene prerrequisito. Al estar basado en SAP Document AI, pueden aplicar requisitos comerciales asociados a Document AI según la configuración requerida.</t>
         </is>
       </c>
+      <c r="M3" s="2" t="inlineStr"/>
+      <c r="N3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -9545,18 +9544,18 @@
       <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr"/>
-      <c r="K6" s="2" t="inlineStr"/>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>https://discovery-center.cloud.sap/ai-feature/4be4b091-a23d-4f59-975e-65cb6a4a8fc5/</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>AI Units requeridos. Pricing Details indica uso de AI Estimator para estimar AI Units y costos; se muestra activación mediante AI Units, pero el contenido accesible no dejó un bloque completo de cantidad/costo. Precio final sujeto a la estimación y condiciones comerciales aplicables.</t>
         </is>
       </c>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -9585,18 +9584,18 @@
       <c r="H7" s="2" t="inlineStr"/>
       <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr"/>
-      <c r="K7" s="2" t="inlineStr"/>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>https://discovery-center.cloud.sap/ai-feature/0568e3e9-bef3-46d5-8b51-f519d8838320/</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>AI Units requeridos. En Pricing Details se indica activación mediante “Activate with AI Units”; precio disponible bajo solicitud; duración contractual disponible bajo solicitud; tiene prerrequisito.</t>
         </is>
       </c>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -9625,20 +9624,20 @@
       <c r="H8" s="2" t="inlineStr"/>
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr"/>
-      <c r="K8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>https://discovery-center.cloud.sap/ai-feature/54d5a00e-2519-46da-88fa-b58b4f8ff4dc/</t>
+        </is>
+      </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
+          <t>Esta oferta de IA solo puede adquirirse como parte del paquete 'Joule Premium for Supply Chain Management' y no está disponible por separado; los precios corresponden al paquete completo. Descripción del paquete: impulsa la agilidad de la cadena de suministro con IA premium que optimiza la programación de mantenimiento, mitiga disrupciones en planta y acelera la planificación de transporte, entre otros. Pricing del paquete por métrica 'Users': hasta 39 usuarios → 8 AI Units por métrica (tarifa EUR 7 por AI Unit; EUR 56 por métrica); hasta 200 → 7,2; hasta 550 → 6,5; hasta 1.000 → 5,7; desde 1.000 → 5. Incluye hasta 5.200 requests sin costo adicional; las solicitudes adicionales se cobran en bloques de 1.000 a 2 AI Units.</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
           <t>Joule Premium for Supply Chain Management</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/54d5a00e-2519-46da-88fa-b58b4f8ff4dc/</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>Esta oferta de IA solo puede adquirirse como parte del paquete 'Joule Premium for Supply Chain Management' y no está disponible por separado; los precios corresponden al paquete completo. Descripción del paquete: impulsa la agilidad de la cadena de suministro con IA premium que optimiza la programación de mantenimiento, mitiga disrupciones en planta y acelera la planificación de transporte, entre otros. Pricing del paquete por métrica 'Users': hasta 39 usuarios → 8 AI Units por métrica (tarifa EUR 7 por AI Unit; EUR 56 por métrica); hasta 200 → 7,2; hasta 550 → 6,5; hasta 1.000 → 5,7; desde 1.000 → 5. Incluye hasta 5.200 requests sin costo adicional; las solicitudes adicionales se cobran en bloques de 1.000 a 2 AI Units.</t>
         </is>
       </c>
     </row>
@@ -9669,18 +9668,18 @@
       <c r="H9" s="2" t="inlineStr"/>
       <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr"/>
-      <c r="K9" s="2" t="inlineStr"/>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>https://discovery-center.cloud.sap/ai-feature/825764c4-6de1-4789-bd0c-74243c60854b/</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>Se puede estimar la cantidad aproximada de AI Units y los costos asociados con el AI Estimator. Métrica: Requests (solicitudes); 0,06 AI Units por métrica; tarifa de EUR 7 por AI Unit (EUR 7 por métrica de referencia). Funcionalidad Premium facturada por consumo de AI Units.</t>
         </is>
       </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -9709,18 +9708,18 @@
       <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>https://discovery-center.cloud.sap/ai-feature/3c3c6f7d-7310-47a9-ae52-d7ddd2f0c2f2/</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>Pricing Details muestra métrica Requests / usuario-mes para SAP Joule for Consultants. La información visible indica 35 AI Units por métrica, tarifa de EUR 7 por AI Unit y costo por métrica de EUR 245, con cantidad incluida hasta 22.900 solicitudes.</t>
         </is>
       </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -9749,18 +9748,18 @@
       <c r="H11" s="2" t="inlineStr"/>
       <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="2" t="inlineStr"/>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>https://discovery-center.cloud.sap/ai-feature/4cb78833-492a-43db-abb2-01747e7e4335/</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>AI Units requeridos. Las solicitudes adicionales se cobran en bloques de 1.000 por 2 AI Unit(s). La página permite estimar consumo/costo mediante AI Estimator; precio final sujeto al paquete correspondiente.</t>
         </is>
       </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -9789,18 +9788,18 @@
       <c r="H12" s="2" t="inlineStr"/>
       <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>https://discovery-center.cloud.sap/ai-feature/16fe0c99-25ff-48e2-81e5-f100d4c64767/</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>Pricing Details indica que esta oferta requiere AI Units y solo puede adquirirse como parte del paquete Joule Premium for Financial Management; no está disponible por separado. La página muestra que el paquete está disponible mediante compra de AI Units.</t>
         </is>
       </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -9881,18 +9880,18 @@
       <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr"/>
-      <c r="K14" s="2" t="inlineStr"/>
-      <c r="L14" s="2" t="inlineStr"/>
-      <c r="M14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>https://discovery-center.cloud.sap/ai-feature/84eb743d-acdb-48ff-b933-ec51fe9f5f12/</t>
         </is>
       </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>AI Units requeridos. En Pricing Details se indica activación mediante “Activate with AI Units”; precio disponible bajo solicitud; duración contractual disponible bajo solicitud; tiene prerrequisito.</t>
         </is>
       </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -9921,18 +9920,18 @@
       <c r="H15" s="2" t="inlineStr"/>
       <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="inlineStr"/>
-      <c r="K15" s="2" t="inlineStr"/>
-      <c r="L15" s="2" t="inlineStr"/>
-      <c r="M15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>https://discovery-center.cloud.sap/ai-feature/15213c47-7c33-4787-a97b-d28f3a031c5a/</t>
         </is>
       </c>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>Se puede estimar la cantidad aproximada de AI Units y los costos asociados con el AI Estimator. Métrica: Requests (solicitudes); 0,29 AI Units por métrica; tarifa de EUR 7 por AI Unit (EUR 7 por métrica de referencia). Funcionalidad Premium facturada por consumo de AI Units.</t>
         </is>
       </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -9963,22 +9962,22 @@
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>AI Feature</t>
+          <t>https://discovery-center.cloud.sap/ai-feature/5205d1ac-b2a1-413b-8d5c-a01e22311cad/</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
+          <t>Requiere AI Units. La oferta solo puede adquirirse como parte del paquete Joule Premium for Financial Management y no está disponible por separado; el paquete se adquiere mediante AI Units. Precio bajo solicitud; duración de contrato disponible bajo solicitud. Incluye prerrequisito.</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>AI Feature</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
           <t>Joule Premium for Financial Management</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/5205d1ac-b2a1-413b-8d5c-a01e22311cad/</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>Requiere AI Units. La oferta solo puede adquirirse como parte del paquete Joule Premium for Financial Management y no está disponible por separado; el paquete se adquiere mediante AI Units. Precio bajo solicitud; duración de contrato disponible bajo solicitud. Incluye prerrequisito.</t>
         </is>
       </c>
     </row>
@@ -10113,18 +10112,18 @@
       <c r="H19" s="2" t="inlineStr"/>
       <c r="I19" s="2" t="inlineStr"/>
       <c r="J19" s="2" t="inlineStr"/>
-      <c r="K19" s="2" t="inlineStr"/>
-      <c r="L19" s="2" t="inlineStr"/>
-      <c r="M19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>https://discovery-center.cloud.sap/ai-feature/d2a47a4f-3ea2-4f5b-9bdf-43fc2a3d95f2/</t>
         </is>
       </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>AI Units requeridos. En Pricing Details se indica que la oferta se adquiere como parte de Joule Premium for Supply Chain Management y no por separado; el precio está disponible bajo solicitud. Las solicitudes adicionales se cobran en bloques de 1.000 por 2 AI Unit(s).</t>
         </is>
       </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -10153,18 +10152,18 @@
       <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr"/>
-      <c r="K20" s="2" t="inlineStr"/>
-      <c r="L20" s="2" t="inlineStr"/>
-      <c r="M20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>https://discovery-center.cloud.sap/ai-feature/be5c57fd-4b09-436f-8a63-16362fce5547/</t>
         </is>
       </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>AI Units requeridos. En Pricing Details se indica que la oferta se adquiere como parte de Joule Premium for Financial Management y no por separado; el precio está disponible bajo solicitud. Las solicitudes adicionales se cobran en bloques de 1.000 por 2 AI Unit(s).</t>
         </is>
       </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -10355,20 +10354,20 @@
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>AI Feature</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr"/>
+          <t>https://discovery-center.cloud.sap/ai-feature/d22ae902-3e3d-4c78-9f8e-a656ecd2686d/</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>Requiere AI Units para usar la oferta de IA en el servicio cloud subyacente. El método de activación indicado es “Activate with AI Units”. Precio bajo solicitud; duración de contrato disponible bajo solicitud. Incluye prerrequisito.</t>
+        </is>
+      </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/d22ae902-3e3d-4c78-9f8e-a656ecd2686d/</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>Requiere AI Units para usar la oferta de IA en el servicio cloud subyacente. El método de activación indicado es “Activate with AI Units”. Precio bajo solicitud; duración de contrato disponible bajo solicitud. Incluye prerrequisito.</t>
-        </is>
-      </c>
+          <t>AI Feature</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -10449,18 +10448,18 @@
       <c r="H26" s="2" t="inlineStr"/>
       <c r="I26" s="2" t="inlineStr"/>
       <c r="J26" s="2" t="inlineStr"/>
-      <c r="K26" s="2" t="inlineStr"/>
-      <c r="L26" s="2" t="inlineStr"/>
-      <c r="M26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>https://discovery-center.cloud.sap/ai-feature/cab0dc5c-6c85-4d8e-963a-cad7a64e012a/</t>
         </is>
       </c>
-      <c r="N26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>AI Units requeridos. En Pricing Details se indica que la oferta solo puede comprarse como parte de Joule Premium for Financial Management y no está disponible por separado; precio y duración de contrato bajo solicitud.</t>
         </is>
       </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -10489,18 +10488,18 @@
       <c r="H27" s="2" t="inlineStr"/>
       <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="2" t="inlineStr"/>
-      <c r="K27" s="2" t="inlineStr"/>
-      <c r="L27" s="2" t="inlineStr"/>
-      <c r="M27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>https://discovery-center.cloud.sap/ai-feature/3fd5ea00-34fa-487e-a76a-be112a71220a/</t>
         </is>
       </c>
-      <c r="N27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>AI Units requeridos. En Pricing Details se indica activación mediante “Activate with AI Units”; precio disponible bajo solicitud; duración contractual disponible bajo solicitud; tiene prerrequisito. La página también indica que, para activar esta capacidad, se requieren SAP Document AI, embedded edition y un workspace de SAP Document AI, por lo que pueden aplicar sus detalles de pricing.</t>
         </is>
       </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -10529,18 +10528,18 @@
       <c r="H28" s="2" t="inlineStr"/>
       <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="2" t="inlineStr"/>
-      <c r="K28" s="2" t="inlineStr"/>
-      <c r="L28" s="2" t="inlineStr"/>
-      <c r="M28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>https://discovery-center.cloud.sap/ai-feature/ffd1d0b2-76fc-4e1f-b1fd-523ec82bae54/</t>
         </is>
       </c>
-      <c r="N28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
         <is>
           <t>Pricing Details indica que la función puede agregarse al AI Estimator para estimar la cantidad aproximada de AI Units y costos relacionados. No se muestra un importe fijo visible en la información extraída de la sección.</t>
         </is>
       </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -10569,18 +10568,18 @@
       <c r="H29" s="2" t="inlineStr"/>
       <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="inlineStr"/>
-      <c r="K29" s="2" t="inlineStr"/>
-      <c r="L29" s="2" t="inlineStr"/>
-      <c r="M29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>https://discovery-center.cloud.sap/ai-feature/8e974edb-5d3e-4500-bc00-8549fbf8edd6/</t>
         </is>
       </c>
-      <c r="N29" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
         <is>
           <t>Se puede estimar la cantidad aproximada de AI Units y los costos asociados con el AI Estimator. Métrica: Requests (solicitudes); 0,23 AI Units por métrica; tarifa de EUR 7 por AI Unit (EUR 7 por métrica de referencia). Funcionalidad Premium facturada por consumo de AI Units.</t>
         </is>
       </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -10717,18 +10716,18 @@
       <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr"/>
-      <c r="K32" s="2" t="inlineStr"/>
-      <c r="L32" s="2" t="inlineStr"/>
-      <c r="M32" s="2" t="inlineStr">
+      <c r="K32" s="2" t="inlineStr">
         <is>
           <t>https://discovery-center.cloud.sap/ai-feature/3de36a16-73ca-4df6-94d2-ccd0dc806192/</t>
         </is>
       </c>
-      <c r="N32" s="2" t="inlineStr">
+      <c r="L32" s="2" t="inlineStr">
         <is>
           <t>Pricing Details muestra consumo asociado a AI Units, con cantidad incluida indicada como 0 AI Units; las solicitudes adicionales estarían sujetas al consumo/estimación correspondiente de AI Units. No se muestra un precio unitario fijo en la información visible.</t>
         </is>
       </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -10757,18 +10756,18 @@
       <c r="H33" s="2" t="inlineStr"/>
       <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr"/>
-      <c r="K33" s="2" t="inlineStr"/>
-      <c r="L33" s="2" t="inlineStr"/>
-      <c r="M33" s="2" t="inlineStr">
+      <c r="K33" s="2" t="inlineStr">
         <is>
           <t>https://discovery-center.cloud.sap/ai-feature/e5701d25-2615-49ad-acf3-4f2a6363a206/</t>
         </is>
       </c>
-      <c r="N33" s="2" t="inlineStr">
+      <c r="L33" s="2" t="inlineStr">
         <is>
           <t>Pricing Details indica que la función puede agregarse al estimador para calcular una cantidad aproximada de AI Units y costos relacionados mediante AI Estimator. No se muestra un precio unitario fijo en la información visible de Pricing Details.</t>
         </is>
       </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -10901,20 +10900,20 @@
       <c r="H36" s="2" t="inlineStr"/>
       <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr"/>
-      <c r="K36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>https://discovery-center.cloud.sap/ai-feature/e547d658-368e-426f-986e-97e574bfb475/</t>
+        </is>
+      </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
+          <t>Esta oferta de IA solo puede adquirirse como parte del paquete 'Joule Premium for Financial Management' y no está disponible por separado; los precios corresponden al paquete completo. Descripción del paquete: incrementa la eficiencia de los procesos financieros centrales con IA avanzada que acelera el cierre de periodo, mejora la gobernanza de datos maestros y reduce los días de ventas pendientes (DSO), entre otros. Pricing del paquete por métrica 'Users': hasta 39 usuarios → 8 AI Units por métrica (tarifa EUR 7 por AI Unit; EUR 56 por métrica); hasta 200 → 7,2; hasta 550 → 6,5; hasta 1.000 → 5,7; desde 1.000 → 5. Incluye hasta 5.200 requests sin costo adicional; las solicitudes adicionales se cobran en bloques de 1.000 a 2 AI Units.</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
           <t>Joule Premium for Financial Management</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/e547d658-368e-426f-986e-97e574bfb475/</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>Esta oferta de IA solo puede adquirirse como parte del paquete 'Joule Premium for Financial Management' y no está disponible por separado; los precios corresponden al paquete completo. Descripción del paquete: incrementa la eficiencia de los procesos financieros centrales con IA avanzada que acelera el cierre de periodo, mejora la gobernanza de datos maestros y reduce los días de ventas pendientes (DSO), entre otros. Pricing del paquete por métrica 'Users': hasta 39 usuarios → 8 AI Units por métrica (tarifa EUR 7 por AI Unit; EUR 56 por métrica); hasta 200 → 7,2; hasta 550 → 6,5; hasta 1.000 → 5,7; desde 1.000 → 5. Incluye hasta 5.200 requests sin costo adicional; las solicitudes adicionales se cobran en bloques de 1.000 a 2 AI Units.</t>
         </is>
       </c>
     </row>
@@ -10999,20 +10998,20 @@
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>AI Feature</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr"/>
+          <t>https://discovery-center.cloud.sap/ai-feature/41b32187-96c9-4780-aa15-fc3cdfac1006/</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>Requiere AI Units para usar esta oferta de IA en el servicio cloud subyacente. El método de activación indicado es “Activate with AI Units”. Precio bajo solicitud; duración del contrato disponible bajo solicitud; tiene prerrequisito.</t>
+        </is>
+      </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/41b32187-96c9-4780-aa15-fc3cdfac1006/</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t>Requiere AI Units para usar esta oferta de IA en el servicio cloud subyacente. El método de activación indicado es “Activate with AI Units”. Precio bajo solicitud; duración del contrato disponible bajo solicitud; tiene prerrequisito.</t>
-        </is>
-      </c>
+          <t>AI Feature</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -11043,6424 +11042,24 @@
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>AI Feature</t>
+          <t>https://discovery-center.cloud.sap/ai-feature/2b5df257-bdfd-4396-a48b-a8362b2e02f7/</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
+          <t>Requiere AI Units. La oferta solo puede adquirirse como parte del paquete Joule Premium for Financial Management y no está disponible por separado; el paquete se adquiere mediante AI Units. Precio bajo solicitud; duración de contrato disponible bajo solicitud.</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>AI Feature</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
           <t>Joule Premium for Financial Management</t>
         </is>
       </c>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/2b5df257-bdfd-4396-a48b-a8362b2e02f7/</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr">
-        <is>
-          <t>Requiere AI Units. La oferta solo puede adquirirse como parte del paquete Joule Premium for Financial Management y no está disponible por separado; el paquete se adquiere mediante AI Units. Precio bajo solicitud; duración de contrato disponible bajo solicitud.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L124"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="60" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="60" customWidth="1" min="11" max="11"/>
-    <col width="24" customWidth="1" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Identifier</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Tipo</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Prerequisitos</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Procedimiento</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Próximos Pasos</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Dificultad estimada</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Link</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Estado Setup</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Detail Page</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Estado Initial Setup</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Allocation Run Results</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>J1003</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>AI Feature</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Suscripción de Joule Base y producto base SAP S/4HANA Cloud Public Edition. Revisar prerrequisitos generales de Joule, configuración de SAP Build Work Zone y SAP Cloud Identity Services según la guía de integración de Joule con SAP S/4HANA Cloud Public Edition.</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Seguir la guía de integración de Joule con SAP S/4HANA Cloud Public Edition: preparar la integración con SAP Build Work Zone, exponer contenido de SAP Fiori Launchpad a SAP BTP, configurar confianza/identidad, ejecutar el Joule Booster y validar que Joule quede disponible para el usuario.</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Validar el acceso de los usuarios a Joule y comprobar que la capability de Allocation Run Results aparezca disponible en el contexto de SAP S/4HANA Cloud Public Edition.</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Alta: requiere coordinación de Joule Base, SAP S/4HANA Cloud Public Edition, SAP Build Work Zone, identidad/usuarios y validación funcional.</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/joule/integrating-joule-with-sap/integration-with-sap-s-4hana-cloud-public-edition</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>Initial Setup localizado como recurso en la página de producto; contenido de ayuda obtenido mediante guía SAP Help de integración Joule/S/4HANA Cloud Public Edition.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Sales Order Status Check</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>J1047</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Configuración de capacidad Joule para consulta de estado de pedidos</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Tener SAP S/4HANA Cloud Public Edition y Joule Base habilitado. Los usuarios de ventas deben contar con permisos para consultar pedidos y visualizar información de fulfillment.</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Confirmar habilitación de Joule; validar el acceso de usuarios; probar consultas de estado de pedido; revisar detalles de issues, causas y sugerencias de manejo desde Joule o apps relacionadas.</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Capacitar al equipo comercial en preguntas soportadas, revisar trazabilidad de casos y ajustar roles o autorizaciones si la información de pedidos no aparece correctamente.</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Baja-Media</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/joule/capabilities-guide/sales-order-status-check</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>SAP S/4HANA Cloud Public Edition</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/8e12da05-b0e4-490f-9cf4-0cc2a9482f71/</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>AI-Assisted Search</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>J108</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>AI Feature</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Rol global con privilegios Data Warehouse General y System Information, por ejemplo DW Administrator; tenant de SAP Datasphere en landscape que soporte SAP Business AI; licencia de AI Units; tenant habilitado para SAP Business AI.</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1. Ir a System &gt; Configuration. 2. Abrir la pestaña AI Services. 3. En AI Features, marcar las opciones que se quieren usar. 4. Guardar. 5. Asignar a los usuarios el privilegio global Data Warehouse AI Consumer.</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Los usuarios con el privilegio requerido verán el botón de Joule en la shell bar.</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Media: requiere validación de tenant/landscape, AI Units y configuración de privilegios/roles en SAP Datasphere.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/SAP_DATASPHERE/9f804b8efa8043539289f42f372c4862/1b3fe45f38df4db1a9cda97a5a7bcdaf.html</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>Completado desde el enlace Initial Setup.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="2" t="inlineStr"/>
-      <c r="L4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Processing of Payment Advices with SAP Document AI</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>J1104</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Configuración inicial documental para cuentas por cobrar</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Contar con SAP S/4HANA Cloud Public Edition, integración con SAP Document AI, permisos para Manage Payment Advices y configuración documental para archivos/lenguajes soportados.</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Configurar la integración con SAP Document AI; habilitar el procesamiento asistido; importar archivos de payment advice; revisar datos extraídos; confirmar o corregir el procesamiento.</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Monitorear exactitud, gestionar excepciones, retroalimentar el proceso documental y capacitar a cuentas por cobrar en revisión de resultados.</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/SAP_S4HANA_CLOUD/918bca53037f408f91a2295d04ac16bc/f216e35ab6524291b60f18baf19622a3.html</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>SAP S/4HANA Cloud Public Edition</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/988b6b7c-ac4f-4c5f-be46-0366c7dc5a2e/</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Supplier Confirmation Mass Creation</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>J1114</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Initial Setup inaccesible desde Resources</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Enlace de Initial Setup identificado en Resources, pero no fue posible acceder o recuperar la URL final desde la página dinámica tras reintentos.</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Enlace de Initial Setup identificado en Resources, pero no fue posible acceder o recuperar la URL final desde la página dinámica tras reintentos.</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Enlace de Initial Setup identificado en Resources, pero no fue posible acceder o recuperar la URL final desde la página dinámica tras reintentos.</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>No determinada</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Enlace de Initial Setup identificado en Resources, pero no fue posible acceder o recuperar la URL final desde la página dinámica tras reintentos.</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>SAP S/4HANA Cloud Public Edition</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/b8dfd079-2d74-417a-ad38-8a5251110a4d/</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Process Analyzer‚ Text to Insight</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>J112</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Configuración funcional de analítica de procesos</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Tener SAP Signavio Process Intelligence con datos de proceso cargados, permisos para Process Analyzer y acceso a la capacidad de consulta asistida por IA.</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Abrir Process Analyzer; formular una pregunta en lenguaje natural; revisar el insight generado; ajustar la pregunta si es necesario; guardar o compartir el resultado validado.</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Validar los insights con analistas de proceso, definir buenas prácticas de prompts y monitorear calidad de datos y adopción por usuarios de negocio.</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/signavio-process-transformation-suite/sap-signavio-process-transformation-suite-administration-guide/activate-embedded-ai-capabilities?version=1.0</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr"/>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>SAP Signavio solutions</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/a6dde1d9-6da4-443f-874a-e6eb183e2bd5/</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Electronic Document Error Handling</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>J1137</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>AI Feature</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>El enlace de Initial Setup indica prerequisitos relacionados con Joule Initial Setup y la integración de Joule con SAP S/4HANA Cloud Private Edition para Electronic Document Error Handling.</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Seguir el setup de Joule y la integración indicada para Electronic Document Error Handling; el contenido extraído referencia también la gestión de explicaciones de error de documentos electrónicos.</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>No se indican próximos pasos en el enlace consultado.</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>Media: requiere configuración de Joule y relación con SAP Document and Reporting Compliance/SAP S/4HANA, pero el texto extraído no muestra desarrollo o integración avanzada.</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/SAP_S4HANA_CLOUD/ae0b823738ee4227b7ec12cc4fbf1b4c/769137a7913747e0b2ad2315dd2e9e4f.html</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="2" t="inlineStr"/>
-      <c r="K8" s="2" t="inlineStr"/>
-      <c r="L8" s="2" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Generation of SAP Fiori Elements and SAPUI5 Applications</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>J114</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>AI Feature</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>No aplica. No existe enlace de Initial Setup en la sección Resources de la página consultada.</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>No aplica. No existe enlace de Initial Setup en la sección Resources de la página consultada.</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>No aplica. No existe enlace de Initial Setup en la sección Resources de la página consultada.</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>No evaluable. La página consultada no incluye enlace Initial Setup en Resources.</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>No existe enlace de Initial Setup en la sección Resources de la página consultada.</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr"/>
-      <c r="J9" s="2" t="inlineStr"/>
-      <c r="K9" s="2" t="inlineStr"/>
-      <c r="L9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>BPMN Simulation Insights</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>J1143</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>AI Feature</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>SAP Signavio Process Manager/Modeler con diagramas BPMN y datos de simulación necesarios para costos, duración, frecuencia y recursos. No se identificaron prerequisitos técnicos de activación adicionales en el enlace consultado.</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Usar la función de simulación BPMN para ejecutar y analizar escenarios de proceso; revisar métricas como costos, tiempos de ciclo, recursos y cuellos de botella, y usar los insights generados para apoyar decisiones.</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>No se indican próximos pasos en el enlace consultado.</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>Media: requiere preparar correctamente el modelo BPMN y los parámetros de simulación, pero no se identificó integración técnica avanzada en el enlace consultado.</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/signavio-process-modeler/user-guide/simulating-bpmn-diagrams</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>Resource de Initial Setup localizado en Discovery; enlace de SAP Help relacionado con simulación BPMN.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Generation of SAP Mobile Applications</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>J115</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>AI Feature</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Tener una cuenta global en SAP BTP. Contar con SAP Build Code configurado/suscrito y autorizaciones para usar el entorno de desarrollo.</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Seguir el Initial Setup de SAP Build Code: preparar cuenta/subcuenta BTP, habilitar o suscribir SAP Build Code, configurar usuarios y roles, y acceder al entorno para usar las capacidades móviles asistidas por Joule.</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>No se identificaron próximos pasos específicos adicionales en el contenido accesible; continuar con la creación del proyecto móvil y validación de permisos en SAP Build Code.</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>Media. Requiere configuración inicial de SAP Build Code y roles; el desarrollo móvil puede requerir validaciones adicionales según el stack móvil usado.</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/build_code/d0d8f5bfc3d640478854e6f4e7c7584a/07698d7c31284e4db370acdf017cfd14.html</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="2" t="inlineStr"/>
-      <c r="L11" s="2" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Generation of SAP HANA Applications</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>J116</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>AI Feature</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Tener una cuenta global en SAP BTP. Contar con SAP Build Code configurado/suscrito y permisos necesarios para trabajar con el entorno de desarrollo.</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Seguir el Initial Setup de SAP Build Code: preparar la cuenta y subcuenta de SAP BTP, habilitar/suscribir SAP Build Code, asignar autorizaciones y roles, y acceder al entorno para usar Joule y las herramientas de desarrollo.</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>No se identificaron próximos pasos específicos adicionales en el contenido accesible; continuar con la creación del proyecto SAP HANA en SAP Build Code y validar permisos.</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>Media. Depende de la configuración de SAP BTP/SAP Build Code y de roles, pero el uso de la capacidad se realiza dentro del entorno de desarrollo.</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/build_code/d0d8f5bfc3d640478854e6f4e7c7584a/07698d7c31284e4db370acdf017cfd14.html</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Form Extension in Localization as a Self-Service</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>J117</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>AI Feature</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>El enlace de Initial Setup existe en Resources, pero no fue posible resolver con seguridad el URL exacto del SAP Help Portal desde el contenido accesible.</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>El enlace de Initial Setup existe, pero no fue posible acceder/resolver con seguridad su contenido exacto. No se completa con fuentes alternativas.</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>El enlace de Initial Setup existe, pero no fue posible acceder/resolver con seguridad su contenido exacto.</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>No evaluable: el enlace existe, pero no fue posible acceder/resolver con seguridad su contenido exacto.</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr"/>
-      <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr"/>
-      <c r="K13" s="2" t="inlineStr"/>
-      <c r="L13" s="2" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Settlement Rule Proposal for Asset Capitalization</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>J1182</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Funcionalidad de SAP S/4HANA Cloud Private Edition</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Sistema SAP S/4HANA Cloud Private Edition con el escenario de Asset Accounting/medidas de inversión disponible y autorizaciones para la app relacionada.</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Acceder a la app Manage Settlement Rule Proposal for Investment Measure, generar una propuesta de regla de liquidación, revisarla y editarla si es necesario.</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Validar la propuesta y continuar el proceso de liquidación/capitalización conforme al flujo de negocio.</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/SAP_S4HANA_ON-PREMISE/f5d3e1005efd4e86acf9a65abf428082/d157eb74feab4a83a65004ab30e870d8.html</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>SAP S/4HANA Cloud Private Edition</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/43cfa9f3-485c-4021-8dd1-e1349f471bea/</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>SAP Joule for Developers‚ ABAP AI capabilities</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>J1195</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Configuración de Joule for Developers ABAP en S/4HANA Cloud Private Edition</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Contar con SAP S/4HANA Cloud Private Edition, usuarios desarrolladores autorizados y acceso a la configuración de SAP Joule for Developers, ABAP AI capabilities.</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Configurar Joule for Developers para ABAP AI capabilities, validar entitlements/licencias, asignar usuarios y confirmar el funcionamiento en el entorno de desarrollo ABAP.</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Definir gobierno de uso, revisar resultados generados por IA y monitorear mejoras en productividad y calidad de código.</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/abap-ai/generative-ai-in-abap-cloud/configuring-joule-for-side-by-side</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>SAP S/4HANA Cloud Private Edition</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/795cf9fa-d0cc-42b0-a3d7-52e8067e847d/</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Performance Indicators Recommender</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>J120</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Initial setup Signavio AI + indicadores de proceso</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>SAP Signavio solutions; acceso a procesos o modelos relevantes; roles para business process analyst o process owner; activación comercial mediante AI Units según Pricing Details.</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Activar la capacidad con AI Units; seleccionar el proceso o problema de negocio; solicitar recomendaciones de KPIs/PPIs; revisar indicadores sugeridos; adoptar o ajustar el marco de medición inicial.</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Validar indicadores con stakeholders; conectarlos con datos o event logs disponibles; monitorear desempeño y ajustar indicadores según aprendizaje del proceso.</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/signavio-process-insights/business-content-reference/process-performance-indicators</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>SAP Signavio solutions</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/4be4b091-a23d-4f59-975e-65cb6a4a8fc5/</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Process Recommender</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>J121</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Configuración inicial de recomendación de procesos</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Tener SAP Signavio con acceso a Process Recommender, permisos para consultar/crear modelos y disponibilidad de contenido o repositorio de procesos para adaptar recomendaciones.</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Abrir AI-assisted Process Recommender; describir o seleccionar la necesidad de proceso; revisar modelos recomendados; elegir una alternativa; guardar y adaptar el proceso.</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Comparar la recomendación con la realidad del negocio, ajustar variantes, validar con dueños de proceso y publicar el modelo aprobado.</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/signavio-process-transformation-suite/sap-signavio-process-transformation-suite-administration-guide/activate-embedded-ai-capabilities?version=1.0</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr"/>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>SAP Signavio solutions</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/0568e3e9-bef3-46d5-8b51-f519d8838320/</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Joule with SAP Signavio solutions</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>J127</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Activación Joule con SAP Signavio solutions</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Joule Base o entitlement aplicable; acceso a SAP Signavio Process Intelligence / Process Modeler; usuarios con permisos sobre contenido de procesos, documentos y métricas; configuración inicial de Joule completada.</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Completar setup inicial de Joule; habilitar Joule para SAP Signavio; validar permisos sobre procesos y contenido; probar búsquedas, navegación y comandos de lenguaje natural en Signavio.</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Validar escenarios con usuarios de procesos, revisar calidad de resultados, promover adopción en análisis/modelado y monitorear mejoras de búsqueda y ejecución de tareas.</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/joule/integrating-joule-with-sap/initial-setup</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr"/>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>SAP Signavio solutions</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/c1ed93ca-2efd-4096-8300-613adf55cfef/</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Document Data Extraction</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>J1284</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>AI Feature</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>Acceso a SAP Build Process Automation y a la capacidad de extracción documental descrita para PDFs e imágenes. El texto extraído del enlace de Initial Setup no expone prerequisitos adicionales específicos.</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>Configurar/usar la funcionalidad de Document Data Extraction desde SAP Build Process Automation para extraer información de documentos estructurados o no estructurados. El texto extraído no expone un paso a paso administrativo más detallado.</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>No se indican próximos pasos en el enlace consultado.</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>Media: requiere SAP Build Process Automation y configuración/uso de extracción documental, aunque no se observa integración avanzada en el texto extraído.</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/build-process-automation/sap-build-process-automation/generative-ai?locale=en-US</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr"/>
-      <c r="J19" s="2" t="inlineStr"/>
-      <c r="K19" s="2" t="inlineStr"/>
-      <c r="L19" s="2" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Purchase Order Approvals Reminder</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>J1310</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Configuración funcional de Joule para procurement</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>Contar con SAP S/4HANA Cloud Public Edition, Joule habilitado, workflow de aprobación de órdenes de compra configurado y usuarios/roles de procurement con permisos adecuados.</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>Confirmar configuración base de Joule; revisar workflows de aprobación de órdenes de compra; validar responsables/aprobadores; habilitar o probar la capacidad de recordatorios desde Joule.</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Medir tiempos de aprobación, revisar recordatorios enviados y ajustar reglas de workflow o responsabilidades si se detectan cuellos de botella.</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/joule/capabilities-guide/updating-delivery-dates-for-purchase-orders</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>SAP S/4HANA Cloud Public Edition</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/13b68daa-1ba2-4bfa-b7d3-4f65f4900d07/</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>Conversational Planning</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>J135</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Configuración técnica</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>Configuración de Intelligent Scenario Lifecycle Management (ISLM) requerida para usar IA generativa en Transportation Management (TM). Solicitud de un service key de SAP BTP para el intelligent scenario GENAI_TM_COPL_GPT40. Definición de un perfil de IA generativa de tipo Conversational Planning con sus capacidades (operaciones de planificación). Asignación del perfil al page layout del transportation cockpit y configuración de los field catalogs (campo Conversational Planning Response). Solo disponible en SAP S/4HANA Cloud Private Edition; puede requerir entitlement y autorización adicionales. Ver SAP Note 3573759.</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Solicitar acceso a SAP AI Services en SAP BTP (service key del intelligent scenario GENAI_TM_COPL_GPT40) y completar los pasos de ISLM. Realizar el Customizing de Transportation Management bajo Basic Functions → Generative Artificial Intelligence: definir el perfil de IA generativa de tipo Conversational Planning indicando las capacidades deseadas; asignar el perfil al page layout mediante la app Define Page Layouts for Transportation Cockpit; configurar los field catalogs para mostrar el campo Conversational Planning Response.</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>Probar prompts en el transportation cockpit (p. ej. seleccionar freight orders/freight units por lenguaje natural) y validar las respuestas generadas.</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/SAP_S4HANA_ON-PREMISE/e3dc5400c1cc41d1bc0ae0e7fd9aa5a2/ae5ea1c82b2f48e2874f94783c6ea0ae.html?locale=en-US</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr"/>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>SAP S/4HANA Cloud Private Edition</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/54d5a00e-2519-46da-88fa-b58b4f8ff4dc/</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>Chart Summary</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>J139</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>No disponible</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>El enlace de Initial Setup aparece en Resources, pero no fue posible acceder después de reintentos.</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>El enlace de Initial Setup aparece en Resources, pero no fue posible acceder después de reintentos.</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>No se indican próximos pasos explícitos.</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>No disponible</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/SAP_ANALYTICS_CLOUD/18850a0e13944f53aa8a8b7c094ea29e/8dcc1f1915b241b3a10c8e5b8a76b062.html?version=2026.2</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>SAP Analytics Cloud</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/825764c4-6de1-4789-bd0c-74243c60854b/</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>Document Summary</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>J1394</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>AI Feature</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>Acceso a SAP Cloud ALM y a la aplicación Documents. El enlace consultado indica que SAP Cloud ALM usa capacidades de IA para generar el resumen de contenido de documentos.</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>En la aplicación de documentos de SAP Cloud ALM, usar la capacidad de resumen para generar un resumen del contenido; el resumen generado por IA se muestra sobre el contenido del documento.</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>No se indican próximos pasos en el enlace consultado.</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>Baja: el uso descrito se realiza directamente dentro de la aplicación de documentos y no muestra configuración compleja.</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/cloud-alm/applicationhelp/documents</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="2" t="inlineStr"/>
-      <c r="K23" s="2" t="inlineStr"/>
-      <c r="L23" s="2" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>Joule with SAP Build Work Zone</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>J145</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Initial Setup doble: SAP Build Work Zone standard / advanced edition</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>Entitlement para SAP Build Work Zone standard o advanced edition; SAP Cloud Identity Services / Identity Authentication; roles administrativos como Launchpad_Admin para standard; prerrequisitos de onboarding para advanced; Joule configurado o planificado para integración.</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Para standard edition, configurar entitlement e inicialización de SAP Build Work Zone; para advanced edition, seguir onboarding, prerrequisitos, booster y post-booster configuration; luego habilitar la integración de Joule en el sitio correspondiente.</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Validar el sitio, contenido, roles, acceso móvil y disponibilidad del icono de Joule para los usuarios finales.</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>Media-Alta</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>Standard: https://help.sap.com/docs/WZ_STD/8c8e1958338140699bd4811b37b82ece/fd79b232967545569d1ae4d8f691016b.html ; Advanced: https://help.sap.com/docs/build-work-zone-advanced-edition/sap-build-work-zone-advanced-edition/onboarding-to-sap-build-work-zone-advanced-edition</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>SAP Build Work Zone</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/8be96d98-f16d-41b4-968c-c295043c1d73/</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>SAP Joule for Consultants</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>J146</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Onboarding y aprovisionamiento de SAP Joule for Consultants</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>Contar con SAP AI Units SKU 8019164, SAP Cloud Identity Services, acceso a data centers soportados y permisos de administrador de BTP, Cloud Identity Services y SAP for Me.</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>Revisar entitlements en BTP; crear subaccount; agregar planes Joule foundation y SAP Consulting Capability standard-ga; establecer trust con SAP Cloud Identity Services; suscribirse a SAP Joule for Consultants; ejecutar el Joule Booster; crear role collections; activar el paquete en SAP for Me; asignar grupos y políticas de autorización.</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>Lanzar SAP Joule for Consultants, validar acceso de usuarios, habilitar contenido restringido con S-user si aplica y configurar integración con un proveedor corporativo de identidad cuando sea necesario.</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/joule/serviceguide/provisioning-sap-joule-for-consultants</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr"/>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>SAP Joule for Consultants</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/3c3c6f7d-7310-47a9-ae52-d7ddd2f0c2f2/</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>Script Optimization</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>J147</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Configuración funcional/técnica de optimización de scripts</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>Contar con SAP Integration Suite y acceso a Cloud Integration con artefactos de integración que contengan scripts personalizados.</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Habilitar o validar acceso a capacidades de inteligencia artificial en SAP Integration Suite; seleccionar scripts personalizados para revisión; ejecutar la optimización y revisar recomendaciones generadas.</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Aplicar mejoras aprobadas, probar los iFlows afectados, monitorear rendimiento y documentar lineamientos de scripting para evitar regresiones.</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/integration-suite/sap-integration-suite/artificial-intelligence</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>SAP Integration Suite</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/99357ead-1ee2-4b9d-9b2f-f74d10f09262/</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>Analytical Insights</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>J148</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>AI Feature</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>SAP Analytics Cloud o SAP Business Data Cloud; cuenta SAP Analytics Cloud para usuarios; configuración de Just Ask; integración de Joule con SAP Analytics Cloud/Business Data Cloud; SAP Build Work Zone e identidad/roles provisionados según la guía de Joule.</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>Habilitar la capability Analytical Insights en Joule, integrar SAC/BDC con Joule, sincronizar roles y permisos, provisionar usuarios hacia SAP Build Work Zone usando IPS, indexar datos con Just Ask y probar preguntas en lenguaje natural.</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>Sincronizar roles/permisos, provisionar usuarios, indexar datos de negocio en Just Ask y probar la integración con preguntas desde Joule.</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>Alta: requiere SAC/BDC, Just Ask, SAP Build Work Zone, IPS, roles y configuración de integración con Joule.</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/joule/integrating-joule-with-sap/enable-the-analytical-insights-capability-in-joule</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" s="2" t="inlineStr"/>
-      <c r="K27" s="2" t="inlineStr"/>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>Initial Setup/guía de habilitación localizada por SAP Help para la capability Analytical Insights.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>Master Data Governance</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>J151</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Initial setup MDG + Joule/AI</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>SAP S/4HANA Cloud Private Edition con Master Data Governance activo; dominios de datos maestros y workflow de change requests definidos; roles para solicitantes/revisores; entitlement/autorización de Joule/AI aplicable.</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>Validar configuración base de MDG y workflows; asignar roles; habilitar el uso de Joule/AI para solicitudes de cambio; probar creación o actualización de change requests en lenguaje natural; revisar resultados y aprobación dentro del flujo MDG.</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>Definir criterios de calidad de datos; medir reducción de esfuerzo en creación/revisión; extender gradualmente a dominios de datos maestros priorizados.</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/SAP_S4HANA_ON-PREMISE/6d52de87aa0d4fb6a90924720a5b0549/570ec2d2701545f78e1a3548a8598f5f.html</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>SAP S/4HANA Cloud Private Edition</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/4cb78833-492a-43db-abb2-01747e7e4335/</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>SAP Joule for Developers‚ ABAP AI capabilities</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>J162</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>Suscripción/configuración de Joule for Developers para ABAP</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>Contar con SAP BTP, ABAP environment, derechos/entitlements para SAP Joule for Developers ABAP AI capabilities y roles de administrador/desarrollador necesarios.</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>Suscribirse a SAP Joule for Developers, ABAP AI capabilities; verificar prerrequisitos; configurar la capacidad para uso side-by-side si aplica; asignar usuarios y permisos correspondientes.</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>Validar acceso desde el entorno de desarrollo ABAP, probar casos de asistencia de código y definir lineamientos internos de uso responsable para desarrolladores.</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/abap-ai/generative-ai-in-abap-cloud/subscribing-to-joule-for-developers-abap-ai-capabilities</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>SAP BTP‚ ABAP environment</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/7f373198-9a41-4416-9eed-bdfca445d37a/</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise Architecture Decision Management</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>J1684</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>AI Feature</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>El recurso Initial Setup existe para este registro según la página de detalle. No fue posible extraer texto suficiente del enlace de SAP Help Portal para identificar prerequisitos concretos sin usar otra fuente.</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>No se pudo extraer un procedimiento concreto desde el enlace de Initial Setup sin recurrir a otra fuente.</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>No se pudo extraer información de próximos pasos desde el enlace de Initial Setup.</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>No evaluada: no se extrajo contenido suficiente del enlace de Initial Setup para clasificar la dificultad sin inferir información externa.</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>Initial Setup - SAP Help Portal existe en la Detail Page, pero no fue posible resolver el URL final desde el extractor.</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="2" t="inlineStr"/>
-      <c r="K30" s="2" t="inlineStr"/>
-      <c r="L30" s="2" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>Sales Order Fulfillment Monitoring</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>J169</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>Configuración funcional de monitoreo de fulfillment con Joule</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>Contar con SAP S/4HANA Cloud Private Edition, paquete Joule Premium for Financial Management si aplica, datos de pedidos de venta y usuarios con permisos para consultar fulfillment y ejecutar acciones relacionadas.</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>Habilitar la capacidad; validar el acceso de usuarios comerciales; probar consultas de estado de pedidos y revisión de issues a nivel cabecera e ítem; confirmar navegación hacia apps relacionadas.</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>Monitorear adopción, revisar calidad de resúmenes y recomendaciones, y ajustar procesos para gestionar bloqueos recurrentes de fulfillment.</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>No se pudo resolver URL exacta del enlace Initial Setup desde la página, aunque Resources lista Initial Setup - SAP Help Portal.</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>SAP S/4HANA Cloud Private Edition</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/16fe0c99-25ff-48e2-81e5-f100d4c64767/</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>Inventory Builder</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>J178</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>AI Feature</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>Para capacidades de IA en SAP LeanIX, el contenido accesible indica que se deben revisar prerrequisitos y pasos de activación específicos en Inventory Builder; no fue posible extraer la lista completa desde el enlace con el navegador disponible.</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>Revisar la documentación de SAP LeanIX sobre AI Capabilities/Inventory Builder y activar/configurar la capacidad siguiendo los pasos indicados allí. No se extrajeron pasos detallados adicionales del enlace con el navegador disponible.</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>No se identificaron próximos pasos específicos en el contenido accesible del enlace.</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>Media. Requiere validaciones de SAP LeanIX y activación/configuración de capacidades de IA, pero no necesariamente desarrollo técnico complejo.</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/leanix/ea/ai-capabilities</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" s="2" t="inlineStr"/>
-      <c r="K32" s="2" t="inlineStr"/>
-      <c r="L32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>SAP HANA application migration</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>J180</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>Migración técnica de aplicaciones SAP HANA XS/XSA a CAP</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>Contar con SAP HANA Cloud, proyecto XS Advanced o XS Classic a migrar, entorno de desarrollo soportado y, para conversión con GenAI, configuración de servicios relacionados con SAP Build/SAP AI según aplique.</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>Preparar conectividad al sistema origen; configurar destino BTP; crear dev space con la extensión de migración; ejecutar SAP HANA Application Migration Assistant/Extension; revisar conversión de artefactos XSJSLIB, XSODATA y XSJS hacia CAP.</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>Validar manualmente el resultado convertido, ajustar lógica de servicios, ejecutar pruebas funcionales y preparar despliegue de la aplicación CAP modernizada.</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/hana-cloud/sap-hana-cloud-migration-guide/migrate-xs-advanced-application-to-sap-cap-and-sap-hana-cloud-with-sap-hana-application-migration-assistant-in-visual-studio-code</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr"/>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>SAP HANA Cloud</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/14bbef6b-5d85-4221-bd0e-342f569ef628/</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>UI Generation from Data</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>J193</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>No disponible</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>No existe enlace de Initial Setup en la sección Resources</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>No existe enlace de Initial Setup en la sección Resources</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>No existe enlace de Initial Setup en la sección Resources</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>No aplica</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>No existe enlace de Initial Setup en la sección Resources</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>SAP Build Apps</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/691b7e82-b4ee-41f2-aae3-43b5b81be6f6/</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>Skill Builder</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>J195</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>Configuración de Joule Studio / SAP Build</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>Suscripciones y licencias requeridas para Joule Studio; entorno soportado; acceso a SAP Build/Joule Studio y roles administrativos correspondientes.</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>Revisar los escenarios de setup de Joule Studio. Una opción indicada es ejecutar un booster para conectar Joule con SAP Build Process Automation; luego asignar usuarios a roles y preparar capacidades de IA.</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>Crear, probar y desplegar skills de Joule para operaciones específicas conectadas a procesos o sistemas SAP/no SAP.</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/Joule_Studio/45f9d2b8914b4f0ba731570ff9a85313/b323c5a639a5428eb05fdafcca9bc9df.html</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr"/>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>Joule Studio</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/e93aa292-e7f4-449d-9586-f1a8510d5ab6/</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>Content Creation and Summary</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>J202</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>Configuración administrativa</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>SAP Build Work Zone, advanced edition con rol de administrador. La integración con Joule debe estar habilitada para el subaccount.</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>Desde la consola de administración de SAP Build Work Zone, advanced edition, habilitar las AI Features (sección 'Enabling AI Features') y configurar la integración con Joule, siguiendo la guía de administración del producto.</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>Validar que las capacidades de generación y resumen de contenido aparezcan disponibles en las workpages para los usuarios de negocio.</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/build-work-zone-advanced-edition/sap-build-work-zone-advanced-edition/enabling-ai-features</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr"/>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>SAP Build Work Zone, advanced edition</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/39ef0f64-fc3b-4420-92ee-fa5e052d486b/</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>Process Analyzer‚ Text To Widget</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>J212</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>Configuración funcional de dashboard asistido por IA</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>Tener SAP Signavio Process Intelligence, dashboards o análisis disponibles, datos de proceso cargados y permisos para crear o modificar widgets.</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>Abrir el dashboard o análisis; usar la opción de generación de widget con lenguaje natural; describir la visualización requerida; revisar el widget generado; ajustar y guardar.</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>Validar widgets con usuarios de negocio, estandarizar prompts útiles, gobernar la publicación de dashboards y monitorear consistencia de métricas.</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/signavio-process-transformation-suite/sap-signavio-process-transformation-suite-administration-guide/activate-embedded-ai-capabilities?version=1.0</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr"/>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>SAP Signavio solutions</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/6d74c5e9-32c1-443c-be23-c7ebbc51d573/</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>Process Modeler</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>J213</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>Configuración inicial de modelado BPMN asistido por IA</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>Contar con SAP Signavio, permisos para modelado de procesos, acceso a la capacidad AI-assisted Process Modeler y AI Units/entitlement correspondiente al uso Premium.</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>Abrir Process Modeler; iniciar la creación asistida por texto; describir el proceso de negocio; generar el modelo BPMN; revisar, refinar y guardar el diagrama.</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>Validar el modelo con stakeholders, completar detalles del proceso, publicar o compartir el diagrama y establecer gobierno de versiones.</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/signavio-process-transformation-suite/sap-signavio-process-transformation-suite-administration-guide/activate-embedded-ai-capabilities?version=1.0</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr"/>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>SAP Signavio solutions</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/84eb743d-acdb-48ff-b933-ec51fe9f5f12/</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>Database Administration</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>J214</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>Configuración de servicio</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>Suscripción a las SAP HANA Cloud Administration Tools (acceso a SAP HANA Cloud Central). La disponibilidad de Gen AI depende del despliegue del production center y del resource plan; ver SAP Notes 3491182 y 3437766.</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>En SAP HANA Cloud Central, seleccionar el icono de Gen AI. Usar Gen AI para tareas de navegación y transaccionales: crear una nueva instancia de SAP HANA Cloud (p. ej. un data lake) a través del asistente de aprovisionamiento, navegar a una app específica (p. ej. el Consumption Monitor), generar resúmenes de alertas, generar sentencias SQL a partir de texto y responder preguntas sobre SAP HANA Cloud.</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>Revisar la disponibilidad de Gen AI según región y resource plan; no se indican próximos pasos adicionales explícitos.</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/HANA_CLOUD/9ae9104a46f74a6583ce5182e7fb20cb/3ec50257efcf49adacebd37babb7455c.html</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr"/>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>SAP HANA Cloud</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/28b14ec8-e7be-4966-b33e-787021b2d05d/</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>Content Generation for Catalog</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>J224</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>Configuración de servicio</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>Disponer de un rol global que otorgue los privilegios Data Warehouse General (-R------), para acceder a SAP Datasphere, y System Information (-RU-----), para acceder al área de Configuration en la herramienta System.</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>En SAP Datasphere, dentro de Administering SAP Datasphere → área System → Configuration, habilitar SAP Business AI y Joule para SAP Datasphere, integrando así las recomendaciones de contenido de IA en el catálogo.</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>Validar la generación de descripciones, términos de negocio y KPIs, así como el auto-tagging de los activos en el catálogo.</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/SAP_DATASPHERE/9f804b8efa8043539289f42f372c4862/1b3fe45f38df4db1a9cda97a5a7bcdaf.html?locale=en-US</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr"/>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>SAP Datasphere</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/15213c47-7c33-4787-a97b-d28f3a031c5a/</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise Search</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>J225</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>AI Feature</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>No existe enlace de Initial Setup en la sección Resources.</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>No existe enlace de Initial Setup en la sección Resources.</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>No existe enlace de Initial Setup en la sección Resources.</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>No evaluable: no existe enlace de Initial Setup en la sección Resources.</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr"/>
-      <c r="I41" s="2" t="inlineStr"/>
-      <c r="J41" s="2" t="inlineStr"/>
-      <c r="K41" s="2" t="inlineStr"/>
-      <c r="L41" s="2" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>Smart Personalization of My Home</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>J226</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Autorización y habilitación en SAP S/4HANA Cloud Public Edition</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>Sistema SAP S/4HANA Cloud Public Edition; asignar a los usuarios autorización mediante IAM app SAP Business AI - User Interface Features - Smart Personalization (F8555_TRAN) o el catálogo equivalente.</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>Abrir Maintain Business Roles, asignar la IAM app/catálogo correspondiente al rol de negocio y dejar habilitada la capacidad para los usuarios objetivo.</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>Los usuarios pueden usar Add Content en My Home, ir a Insights Cards, escribir una consulta en lenguaje natural, generar/previsualizar la tarjeta y agregarla.</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/SAP_S4HANA_CLOUD/4fc8d03390c342da8a60f8ee387bca1a/3b78db8727f541ab88e59f9c44f4c377.html</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>SAP S/4HANA Cloud Public Edition</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/5205d1ac-b2a1-413b-8d5c-a01e22311cad/</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>Error Explanation</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>J227</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>AI Feature</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>El enlace de Initial Setup fue localizado; el contenido accesible indica que se debe iniciar sesión como administrador en SAP Fiori launchpad del sistema SAP S/4HANA Cloud Public Edition.</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>Seguir la página de SAP Help Portal “Enabling the AI-Assisted Error Explanation”. El contenido extractable disponible confirma el inicio como administrador; no se agregan pasos adicionales no verificados.</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>No se indican próximos pasos en el enlace consultado.</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>Media: requiere acceso administrativo y activación/configuración en SAP Fiori launchpad.</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/SAP_S4HANA_CLOUD/4fc8d03390c342da8a60f8ee387bca1a/fbcd177357284dd5846347f04e1cea67.html</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr"/>
-      <c r="J43" s="2" t="inlineStr"/>
-      <c r="K43" s="2" t="inlineStr"/>
-      <c r="L43" s="2" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>In-house Service Initiation</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>J240</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>AI Feature</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>El contenido accesible de SAP Help para In-House Service incluye secciones de prerrequisitos como acceso al sistema, roles, datos maestros y datos organizacionales.</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>Configurar y usar el proceso de In-House Service según la documentación de SAP: asegurar acceso, roles y datos maestros/organizacionales; luego utilizar la función de creación de servicio interno desde documentos cuando aplique.</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>Continuar con la configuración funcional de In-House Service y validación de las apps/roles asociadas. No se extrajeron próximos pasos específicos adicionales del enlace.</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>Alta. Requiere configuración funcional de Service, roles, datos maestros y probablemente coordinación con procesos/documentos de reparación.</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/SAP_S4HANA_ON-PREMISE/c9b5e9de6e674fb99fff88d72c352291/f437d220829a4334976cd81c3b055a04.html</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="2" t="inlineStr"/>
-      <c r="K44" s="2" t="inlineStr"/>
-      <c r="L44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>Maintenance Order Recommendation</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>J241</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>Initial setup de feature AI en mantenimiento</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>SAP S/4HANA Cloud Private Edition; historial suficiente de órdenes de mantenimiento; roles de maintenance planner; acceso a la app de mantenimiento correspondiente; entitlement/autorización para la recomendación asistida por IA.</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>Validar roles y disponibilidad de datos históricos; abrir el flujo de creación o gestión de órdenes de mantenimiento; solicitar o revisar recomendaciones de órdenes similares; seleccionar la orden más adecuada como referencia; copiarla para crear la nueva orden.</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>Monitorear calidad de recomendaciones; depurar datos históricos y maestros; capacitar planners en revisión de recomendaciones antes de copiar órdenes.</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/SAP_S4HANA_ON-PREMISE/e72f747389b340229f7fa343975bfa57/46af82ff1a4e47159f6cc00a06b94e91.html</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr"/>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>SAP S/4HANA Cloud Private Edition</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/d2a47a4f-3ea2-4f5b-9bdf-43fc2a3d95f2/</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>API traffic prediction</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>J243</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>AI Feature</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>APIs en SAP Integration Suite/API Management con historial mínimo de volumen de llamadas API. La documentación indexada indica requisito mínimo de al menos 3 meses de datos de volumen de llamadas API.</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>Usar la sección Predictions de SAP Integration Suite para trabajar con APIs que cumplen el requisito mínimo, seleccionando opciones configurables de predicción según APIs/proxies y horizonte/frecuencia disponibles.</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>No se indican próximos pasos en el enlace consultado.</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>Media: depende de calidad/histórico de datos API y configuración de opciones de predicción.</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/integration-suite/sap-integration-suite/predictions</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" s="2" t="inlineStr"/>
-      <c r="K46" s="2" t="inlineStr"/>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t>Initial Setup/guía SAP Help localizada para Predictions.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>Journal Upload</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>J247</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>Initial setup funcional + configuración de políticas de contabilización</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>SAP S/4HANA Cloud Private Edition; entitlement/autorización para la capacidad AI-assisted Journal Upload; roles de contabilidad y acceso a apps Fiori de Journal Upload/Posting Policies; políticas o documentos guía de contabilización disponibles para configurar el comportamiento de la propuesta.</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>Asignar roles y accesos; configurar o cargar la política/guía de contabilización en Manage Journal Posting Policies; crear un Journal Upload Case; cargar o preparar datos de contabilización; generar la propuesta con IA; revisar, validar y publicar el asiento.</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>Probar con casos controlados de cierre; revisar logs y trazabilidad; ajustar políticas de contabilización; definir controles de aprobación antes de uso productivo.</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>Media-Alta</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/SAP_S4HANA_ON-PREMISE/651d8af3ea974ad1a4d74449122c620e/7d5b6268b58442669a6a4a50fff58a01.html</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr"/>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>SAP S/4HANA Cloud Private Edition</t>
-        </is>
-      </c>
-      <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/be5c57fd-4b09-436f-8a63-16362fce5547/</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>Natural Language Query</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>J25</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>No existe enlace de Initial Setup en la sección Resources</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>No existe enlace de Initial Setup en la sección Resources</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>No existe enlace de Initial Setup en la sección Resources</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>No existe enlace de Initial Setup en la sección Resources</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>No aplica</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>No existe enlace de Initial Setup en la sección Resources</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>SAP Analytics Cloud</t>
-        </is>
-      </c>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/6a655660-1f00-4b22-a6e4-b79167b527ec/</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>AI-Assisted Commenting</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>J275</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>AI Feature</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>El tenant de SAP Analytics Cloud debe estar en un data center que soporte SAP Business AI. Se consumen AI Units y el balance puede revisarse en SAP for Me.</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>1. Iniciar sesión en SAP for Me. 2. En el panel de navegación, elegir Portfolio &amp; Products. 3. Elegir Business AI. 4. Seleccionar Request Activation junto al nombre de la feature.</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>SAP Support notificará cuando la feature haya sido activada.</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>Media: depende de data center compatible, AI Units y solicitud formal de activación mediante SAP for Me/SAP Support.</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/SAP_ANALYTICS_CLOUD/00f68c2e08b941f081002fd3691d86a7/8dcc1f1915b241b3a10c8e5b8a76b062.html</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>Completado desde el enlace Initial Setup.</t>
-        </is>
-      </c>
-      <c r="J49" s="2" t="inlineStr"/>
-      <c r="K49" s="2" t="inlineStr"/>
-      <c r="L49" s="2" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>Goods Receipt Processing</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>J28</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>AI Feature</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>El contenido accesible confirma la existencia de AI-Assisted Goods Receipt Analysis y su uso para revisar documentos con IA; no fue posible extraer una lista completa de prerrequisitos desde el enlace con el navegador disponible.</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>El contenido accesible describe la revisión automática de documentos de entrega usando IA. No fue posible extraer pasos detallados de procedimiento desde el enlace con el navegador disponible.</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>No se identificaron próximos pasos específicos en el contenido accesible del enlace.</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>Alta. Aunque la capacidad automatiza el análisis, se relaciona con procesos de SAP S/4HANA Cloud Private Edition / Transportation Management y puede requerir configuración funcional, escenarios inteligentes, roles y validaciones de proceso.</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/SAP_S4HANA_ON-PREMISE/e3dc5400c1cc41d1bc0ae0e7fd9aa5a2/30d87325d6964ec18da12bd2fe927009.html</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr"/>
-      <c r="J50" s="2" t="inlineStr"/>
-      <c r="K50" s="2" t="inlineStr"/>
-      <c r="L50" s="2" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>Joule with SAP LeanIX</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>J284</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>Configuración inicial de Joule / integración de producto SAP</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>Contar con SAP BTP cockpit y subcuenta para Joule; tener la suscripción/entitlement aplicable de Joule; disponer de SAP Cloud Identity Services / Identity Authentication configurado; contar con permisos administrativos para ejecutar el setup e integrar la solución SAP correspondiente.</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>Revisar prerrequisitos; acceder a SAP BTP cockpit; ejecutar el booster/configuración inicial de Joule cuando aplique; seleccionar la ruta de integración correspondiente; configurar confianza, roles, destinos o formación requerida; activar Joule y validar que el icono/experiencia quede disponible para usuarios autorizados.</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>Validar acceso con usuarios de prueba, revisar permisos y escenarios disponibles, completar la integración específica del producto, comunicar adopción a usuarios y monitorear uso/soporte.</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/joule/integrating-joule-with-sap/initial-setup</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="inlineStr"/>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>SAP LeanIX solutions</t>
-        </is>
-      </c>
-      <c r="K51" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/afef2f21-b812-4548-ab8a-cec5f8fedb10/</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>Explanation of Fixed Asset Key Figures</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>J288</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>AI Feature</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>El enlace de Initial Setup existe en Resources. El enlace de SAP Help Portal corresponde a AI-Generated Explanation of Key Figures; el contenido disponible indica el uso en la sección Value Display de la app Manage Fixed Assets.</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>Usar la funcionalidad desde la sección Value Display de la app Manage Fixed Assets para visualizar y explicar key figures del activo fijo. No se agregan pasos adicionales no verificados.</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>No se indican próximos pasos en el enlace consultado.</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>Media: requiere acceso a la app Manage Fixed Assets y a la funcionalidad habilitada para explicar key figures.</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/SAP_S4HANA_CLOUD/ee9ee0ca4c3942068ea584d2f929b5b1/ee5966f4b7f640ac8edbe3aa26bcc47b.html</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr"/>
-      <c r="J52" s="2" t="inlineStr"/>
-      <c r="K52" s="2" t="inlineStr"/>
-      <c r="L52" s="2" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>Joule with SAP Datasphere</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>J294</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>Integración Joule + SAP Datasphere + Work Zone/IPS</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>Joule inicial configurado; SAP Datasphere tenant; SAP Build Work Zone cuando aplique para integración; usuarios, roles y permisos sincronizables; acceso a Identity Provisioning Service para aprovisionamiento.</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>Crear formación de integración con SAP Build Work Zone; seleccionar sistemas SAP Datasphere y Work Zone; validar content provider; configurar aprovisionamiento de usuarios/roles con IPS; ejecutar simulación y sincronización.</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>Validar acceso de usuarios a contenido de SAP Datasphere en Joule, automatizar sincronización de usuarios y revisar escenarios informativos/navegacionales habilitados.</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/joule/integrating-joule-with-sap/initial-setup</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr"/>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>SAP Datasphere</t>
-        </is>
-      </c>
-      <c r="K53" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/a2bc2dd0-4f0b-4d82-9f94-c3baaac6c83b/</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>Creation of Fixed Asset Master Data</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>J298</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>Configuración técnica</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>Joule Base habilitado y producto base SAP S/4HANA Cloud Public Edition. Integración de Joule preparada (SAP BTP, SAP Build Work Zone, identidad/usuarios) según la guía de integración de Joule con SAP S/4HANA Cloud Public Edition.</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>Seguir la guía de integración de Joule con SAP S/4HANA Cloud Public Edition: exponer el contenido del SAP Fiori Launchpad a SAP BTP; registrar el sistema SAP S/4HANA Cloud Public Edition; configurar el Identity Provisioning Service; mantener la Custom Content Security Policy; habilitar el icono de Joule en el SAP Fiori Launchpad.</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>Validar el acceso de los usuarios a Joule y comprobar que la capability de creación de datos maestros de activos fijos quede disponible.</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/joule/integrating-joule-with-sap/integration-with-sap-s-4hana-cloud-public-edition?locale=en-US</t>
-        </is>
-      </c>
-      <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>SAP S/4HANA Cloud Public Edition</t>
-        </is>
-      </c>
-      <c r="K54" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/095edf47-cb36-48d8-bd8f-9a4bc9517991/</t>
-        </is>
-      </c>
-      <c r="L54" s="2" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>Electronic Document Error Handling</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>J305</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>AI Feature</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>El enlace de Initial Setup indica prerequisitos relacionados con Joule Initial Setup y la integración de Joule con SAP S/4HANA Cloud Private Edition para Electronic Document Error Handling.</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>Seguir el setup de Joule y la integración indicada para Electronic Document Error Handling; el contenido extraído referencia también la gestión de explicaciones de error de documentos electrónicos.</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>No se indican próximos pasos en el enlace consultado.</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>Media: requiere configuración de Joule y relación con SAP Document and Reporting Compliance/SAP S/4HANA, pero el texto extraído no muestra desarrollo o integración avanzada.</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/SAP_S4HANA_CLOUD/ae0b823738ee4227b7ec12cc4fbf1b4c/769137a7913747e0b2ad2315dd2e9e4f.html</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="inlineStr"/>
-      <c r="J55" s="2" t="inlineStr"/>
-      <c r="K55" s="2" t="inlineStr"/>
-      <c r="L55" s="2" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>Agent Builder</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>J308</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>AI Feature</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>No completado: no fue posible resolver el URL exacto de “Initial Setup - SAP Help Portal” desde el contenido accesible. No se usó otra fuente para completar prerequisitos.</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>No completado: no fue posible resolver el URL exacto de “Initial Setup - SAP Help Portal” desde el contenido accesible. No se usó otra fuente para completar procedimiento.</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>No completado: no fue posible resolver el URL exacto de “Initial Setup - SAP Help Portal” desde el contenido accesible. No se usó otra fuente para completar próximos pasos.</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>No determinada: el enlace de Initial Setup no fue accesible/resuelto en el contenido consultado.</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>No disponible — URL exacto no resuelto</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>Initial Setup no resuelto; no se rellenó con otra fuente.</t>
-        </is>
-      </c>
-      <c r="J56" s="2" t="inlineStr"/>
-      <c r="K56" s="2" t="inlineStr"/>
-      <c r="L56" s="2" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>Expiring Price Handling</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>J313</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>AI Feature</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>El enlace de Initial Setup existe en Resources. La página de SAP Help Portal corresponde a la capacidad Expiring Price Handling de Joule. El contenido completo no fue totalmente extractable, por lo que no se agregan prerequisitos no verificados.</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>Seguir la página de SAP Help Portal de Expiring Price Handling. No se agregan pasos adicionales no verificados porque el contenido completo de procedimiento no fue totalmente extractable.</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>No se indican próximos pasos en el enlace consultado.</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>Media: depende de tener Joule/capacidad habilitada y configuración de pricing, pero el procedimiento detallado no fue completamente extractable.</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/joule/capabilities-guide/renew-expiring-prices</t>
-        </is>
-      </c>
-      <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" s="2" t="inlineStr"/>
-      <c r="K57" s="2" t="inlineStr"/>
-      <c r="L57" s="2" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>Meeting Location Planner Agent</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>J326</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>No existe enlace de Initial Setup en la sección Resources</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>No existe enlace de Initial Setup en la sección Resources</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>No existe enlace de Initial Setup en la sección Resources</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>No existe enlace de Initial Setup en la sección Resources</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>No aplica</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>No existe enlace de Initial Setup en la sección Resources</t>
-        </is>
-      </c>
-      <c r="I58" s="2" t="inlineStr"/>
-      <c r="J58" s="2" t="inlineStr"/>
-      <c r="K58" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/65b25edc-21cc-4b54-8f3c-eb4524ab3117/</t>
-        </is>
-      </c>
-      <c r="L58" s="2" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>Expense Report Validation Agent</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>J327</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>AI Agent</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>No existe enlace de Initial Setup en la sección Resources.</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>No existe enlace de Initial Setup en la sección Resources.</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>No existe enlace de Initial Setup en la sección Resources.</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t>No evaluable: no existe enlace de Initial Setup en la sección Resources.</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr"/>
-      <c r="I59" s="2" t="inlineStr"/>
-      <c r="J59" s="2" t="inlineStr"/>
-      <c r="K59" s="2" t="inlineStr"/>
-      <c r="L59" s="2" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>Semantic Generation</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>J329</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>Configuración de SAP Datasphere / habilitación de SAP Business AI</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>Tenant de SAP Datasphere con permisos de administración; habilitación de servicios de IA/AI Features y disponibilidad comercial mediante AI Units.</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>Desde System Configuration en SAP Datasphere, revisar la pestaña AI Services y habilitar las AI Features requeridas para SAP Business AI.</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>Usar la generación semántica sobre entidades/tablas no SAP para crear o completar información semántica como medidas, dimensiones, unidades y asociaciones.</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/SAP_DATASPHERE/9f804b8efa8043539289f42f372c4862/1b3fe45f38df4db1a9cda97a5a7bcdaf.html</t>
-        </is>
-      </c>
-      <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>SAP Datasphere</t>
-        </is>
-      </c>
-      <c r="K60" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/d22ae902-3e3d-4c78-9f8e-a656ecd2686d/</t>
-        </is>
-      </c>
-      <c r="L60" s="2" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>Error Resolution for Cost Accounting</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>J336</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>AI Feature</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>No existe enlace de Initial Setup en la sección Resources.</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>No existe enlace de Initial Setup en la sección Resources.</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>No existe enlace de Initial Setup en la sección Resources.</t>
-        </is>
-      </c>
-      <c r="G61" s="2" t="inlineStr">
-        <is>
-          <t>No evaluable: no existe enlace de Initial Setup en la sección Resources.</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="inlineStr"/>
-      <c r="I61" s="2" t="inlineStr"/>
-      <c r="J61" s="2" t="inlineStr"/>
-      <c r="K61" s="2" t="inlineStr"/>
-      <c r="L61" s="2" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>Embedded Edition</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>J342</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>AI Feature</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>El enlace de SAP Document AI indica Initial Setup para suscribirse, acceder y usar la UI básica de SAP Document AI; también referencia el uso de SAP Document AI Workspace para Embedded Edition y Premium Edition.</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>Realizar la configuración inicial de SAP Document AI siguiendo el enlace de Initial Setup: suscripción, acceso y uso de la UI básica / workspace de SAP Document AI según corresponda.</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>No se indican próximos pasos en el enlace consultado.</t>
-        </is>
-      </c>
-      <c r="G62" s="2" t="inlineStr">
-        <is>
-          <t>Media: requiere configuración inicial de SAP Document AI y uso de workspace; puede involucrar suscripción y acceso al servicio.</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/SAP_DOCUMENT_AI</t>
-        </is>
-      </c>
-      <c r="I62" s="2" t="inlineStr"/>
-      <c r="J62" s="2" t="inlineStr"/>
-      <c r="K62" s="2" t="inlineStr"/>
-      <c r="L62" s="2" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>Note Corrections for Project Billing</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>J346</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>Initial setup funcional en Project Billing</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>SAP S/4HANA Cloud Public Edition; uso de Manage Project Billing; ítems de Time &amp; Expenses con notas; roles de billing specialist; entitlement/autorización de Joule Premium for Financial Management o AI Units aplicables.</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>Asignar roles; validar disponibilidad de Smart Notes en Manage Project Billing; abrir ítems con notas; revisar propuestas generadas para corrección gramatical; aceptar, editar o descartar cambios antes de emitir la factura.</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>Medir tiempos de corrección; validar calidad de notas propuestas; definir criterios de revisión para especialistas de facturación.</t>
-        </is>
-      </c>
-      <c r="G63" s="2" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/SAP_S4HANA_CLOUD/29cf986299714386847f4d4c9bb86994/baaa95fc66a147689e80e6527f22c0f9.html</t>
-        </is>
-      </c>
-      <c r="I63" s="2" t="inlineStr"/>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t>SAP S/4HANA Cloud Public Edition</t>
-        </is>
-      </c>
-      <c r="K63" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/cab0dc5c-6c85-4d8e-963a-cad7a64e012a/</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>Posting Issue Handling for Billing Documents</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>J355</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>No existe enlace de Initial Setup en la sección Resources</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>No existe enlace de Initial Setup en la sección Resources</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>No existe enlace de Initial Setup en la sección Resources</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>No existe enlace de Initial Setup en la sección Resources</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t>No aplica</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>No existe enlace de Initial Setup en la sección Resources</t>
-        </is>
-      </c>
-      <c r="I64" s="2" t="inlineStr"/>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>SAP S/4HANA Cloud Public Edition</t>
-        </is>
-      </c>
-      <c r="K64" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/f558354e-8de3-4b95-ae75-4cc5055cf911/</t>
-        </is>
-      </c>
-      <c r="L64" s="2" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>Processing of Incoming Quality Certificates with SAP Document AI</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>J358</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>Configuración inicial documental integrada a S/4HANA</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>Contar con SAP S/4HANA Cloud Public Edition, SAP Document AI embedded edition, workspace de SAP Document AI, permisos de técnico de calidad y documentos de certificados de calidad de entrada.</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>Configurar SAP Document AI y su workspace; habilitar la integración para certificados de calidad; cargar el certificado; ejecutar extracción y matching; revisar excepciones y actualizar o crear el certificate receipt.</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t>Monitorear exactitud de extracción, ajustar el workspace/esquema documental, entrenar usuarios y controlar impactos en liberación de stock.</t>
-        </is>
-      </c>
-      <c r="G65" s="2" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/document-ai/sap-document-ai/initial-setup</t>
-        </is>
-      </c>
-      <c r="I65" s="2" t="inlineStr"/>
-      <c r="J65" s="2" t="inlineStr">
-        <is>
-          <t>SAP S/4HANA Cloud Public Edition</t>
-        </is>
-      </c>
-      <c r="K65" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/3fd5ea00-34fa-487e-a76a-be112a71220a/</t>
-        </is>
-      </c>
-      <c r="L65" s="2" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>Generation of Full-Stack Applications</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>J36</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>AI Feature</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>Tener una cuenta global en SAP BTP. Contar con la suscripción/configuración de SAP Build Code y autorizaciones necesarias para administrar el servicio y los usuarios.</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>Seguir el Initial Setup de SAP Build Code: preparar la cuenta/subcuenta de SAP BTP, habilitar o suscribir SAP Build Code según el plan disponible, configurar acceso de usuarios y roles, y abrir SAP Build Code para usar las capacidades de desarrollo asistidas por Joule.</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>No se identificaron próximos pasos específicos adicionales en el contenido accesible del enlace; continuar con la configuración de roles y uso del entorno según la guía de SAP Build Code.</t>
-        </is>
-      </c>
-      <c r="G66" s="2" t="inlineStr">
-        <is>
-          <t>Media. Requiere configuración en SAP BTP, suscripción/entitlement del servicio y asignación de roles, pero no implica una integración técnica compleja adicional para esta capacidad.</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/build_code/d0d8f5bfc3d640478854e6f4e7c7584a/07698d7c31284e4db370acdf017cfd14.html</t>
-        </is>
-      </c>
-      <c r="I66" s="2" t="inlineStr"/>
-      <c r="J66" s="2" t="inlineStr"/>
-      <c r="K66" s="2" t="inlineStr"/>
-      <c r="L66" s="2" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>Sales Order Creation from Unstructured Data</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>J404</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>Configuración funcional de Create Sales Orders from Unstructured Data</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>Contar con SAP S/4HANA Cloud Public Edition, alcance/proceso de creación de pedidos desde datos no estructurados y usuarios de ventas con permisos para cargar y procesar archivos.</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>Activar o validar el proceso indicado en Initial Setup; preparar la app de creación de pedidos con extracción automática; cargar documentos PDF o imagen; revisar campos propuestos y confirmar la creación de solicitudes de pedido.</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>Validar casos de prueba con órdenes reales, ajustar datos maestros y capacitar a los representantes internos de ventas en revisión de propuestas antes de convertirlas en pedidos.</t>
-        </is>
-      </c>
-      <c r="G67" s="2" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t>No se pudo resolver URL exacta del enlace Initial Setup desde la página; la página lista Initial Setup - Step 1 y Step 2 en Resources.</t>
-        </is>
-      </c>
-      <c r="I67" s="2" t="inlineStr"/>
-      <c r="J67" s="2" t="inlineStr">
-        <is>
-          <t>SAP S/4HANA Cloud Public Edition</t>
-        </is>
-      </c>
-      <c r="K67" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/ffd1d0b2-76fc-4e1f-b1fd-523ec82bae54/</t>
-        </is>
-      </c>
-      <c r="L67" s="2" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>Sales Order Automatic Completion</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>J43</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>Configuración de ML para completitud de órdenes de venta</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>Contar con SAP S/4HANA Cloud Public Edition, datos históricos suficientes de órdenes de venta, modelo SLS_DOC_AUTO_COMPLTN entrenado y configuración de ventas habilitada.</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>Asegurar entrenamiento del modelo; validar configuración de sales documents; abrir la app de monitoreo/recomendaciones; revisar propuestas para completar solicitudes u órdenes incompletas.</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>Monitorear precisión de recomendaciones, revisar casos rechazados y reentrenar/ajustar configuración si cambian patrones de ventas.</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/SAP_S4HANA_CLOUD/a376cd9ea00d476b96f18dea1247e6a5/1a0d71eb945e48caa72e7ad822017121.html</t>
-        </is>
-      </c>
-      <c r="I68" s="2" t="inlineStr"/>
-      <c r="J68" s="2" t="inlineStr">
-        <is>
-          <t>SAP S/4HANA Cloud Public Edition</t>
-        </is>
-      </c>
-      <c r="K68" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/39a49e49-3ab6-46f5-889d-2035d9378cab/</t>
-        </is>
-      </c>
-      <c r="L68" s="2" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>Inventory Prompts</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>J45</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>AI Feature</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>La documentación accesible de SAP LeanIX AI Capabilities menciona capacidades base de IA, incluyendo Inventory AI prompts. No fue posible extraer una lista completa de prerrequisitos desde el enlace con el navegador disponible.</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>Consultar AI Capabilities en SAP LeanIX y activar/configurar Inventory AI prompts de acuerdo con la guía correspondiente. No se extrajeron pasos detallados adicionales del enlace con el navegador disponible.</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>No se identificaron próximos pasos específicos en el contenido accesible del enlace.</t>
-        </is>
-      </c>
-      <c r="G69" s="2" t="inlineStr">
-        <is>
-          <t>Media. Depende de habilitación/configuración de capacidades de IA en SAP LeanIX y validación de permisos, pero el uso se realiza desde la interfaz de LeanIX.</t>
-        </is>
-      </c>
-      <c r="H69" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/leanix/ea/ai-capabilities</t>
-        </is>
-      </c>
-      <c r="I69" s="2" t="inlineStr"/>
-      <c r="J69" s="2" t="inlineStr"/>
-      <c r="K69" s="2" t="inlineStr"/>
-      <c r="L69" s="2" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>Context Generation</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>J46</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>Activación de funcionalidad</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>SAP LeanIX con las AI capabilities habilitadas en el workspace (Base AI capabilities). La página no indica prerrequisitos técnicos adicionales explícitos; rige la gobernanza de IA de SAP (enfoque human-in-the-loop, sin uso de datos del workspace para entrenar modelos).</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>Las Base AI capabilities de SAP LeanIX —entre ellas el AI-generated context— están embebidas en la interfaz del inventory y del workspace. El contexto generado por IA se presenta como asistencia contextual durante los flujos de trabajo, con etiquetas/iconos de IA que indican el contenido generado; no requiere configuración técnica avanzada del lado del usuario.</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>No se indican próximos pasos explícitos.</t>
-        </is>
-      </c>
-      <c r="G70" s="2" t="inlineStr">
-        <is>
-          <t>Baja</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>https://docs-eam.leanix.net/docs/ai-capabilities</t>
-        </is>
-      </c>
-      <c r="I70" s="2" t="inlineStr"/>
-      <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t>SAP LeanIX solutions</t>
-        </is>
-      </c>
-      <c r="K70" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/fa2762c1-5080-480b-bf93-103933a0af11/</t>
-        </is>
-      </c>
-      <c r="L70" s="2" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>AI-Assisted Texting</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>J47</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>AI Feature</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>SAP AI terms incluidos para nuevos clientes. Si el contrato no está firmado y se quieren activar capacidades de IA, se debe contactar al representante SAP. El contenido accesible no expone más detalle de prerequisitos.</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>El enlace de setup accesible identifica activación de AI Capabilities para SAP LeanIX, pero el extracto disponible no expone el procedimiento completo. No se completó con otras fuentes.</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>No se indican próximos pasos en el contenido accesible del enlace consultado.</t>
-        </is>
-      </c>
-      <c r="G71" s="2" t="inlineStr">
-        <is>
-          <t>Media: requiere validación contractual/activación de capacidades AI; el procedimiento completo no quedó expuesto en el contenido accesible.</t>
-        </is>
-      </c>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/leanix/ea/ai-capabilities</t>
-        </is>
-      </c>
-      <c r="I71" s="2" t="inlineStr">
-        <is>
-          <t>Acceso parcial al enlace Initial Setup; no se complementó con otras fuentes.</t>
-        </is>
-      </c>
-      <c r="J71" s="2" t="inlineStr"/>
-      <c r="K71" s="2" t="inlineStr"/>
-      <c r="L71" s="2" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>Data Actions</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>J470</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>No disponible</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>El enlace de Initial Setup aparece en Resources, pero no fue posible acceder después de reintentos.</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>El enlace de Initial Setup aparece en Resources, pero no fue posible acceder después de reintentos.</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>No se indican próximos pasos explícitos.</t>
-        </is>
-      </c>
-      <c r="G72" s="2" t="inlineStr">
-        <is>
-          <t>No disponible</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/SAP_ANALYTICS_CLOUD/18850a0e13944f53aa8a8b7c094ea29e/8dcc1f1915b241b3a10c8e5b8a76b062.html?version=2025.15</t>
-        </is>
-      </c>
-      <c r="I72" s="2" t="inlineStr"/>
-      <c r="J72" s="2" t="inlineStr">
-        <is>
-          <t>SAP Analytics Cloud</t>
-        </is>
-      </c>
-      <c r="K72" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/8e974edb-5d3e-4500-bc00-8549fbf8edd6/</t>
-        </is>
-      </c>
-      <c r="L72" s="2" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>AI-Assisted Calculations</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>J471</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>AI Feature</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>El tenant de SAP Analytics Cloud debe estar en un data center que soporte SAP Business AI. Se consumen AI Units y el balance puede revisarse en SAP for Me.</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>1. Iniciar sesión en SAP for Me. 2. En el panel de navegación, elegir Portfolio &amp; Products. 3. Elegir Business AI. 4. Seleccionar Request Activation junto al nombre de la feature.</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>SAP Support notificará cuando la feature haya sido activada.</t>
-        </is>
-      </c>
-      <c r="G73" s="2" t="inlineStr">
-        <is>
-          <t>Media: depende de data center compatible, AI Units y solicitud formal de activación mediante SAP for Me/SAP Support.</t>
-        </is>
-      </c>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/SAP_ANALYTICS_CLOUD/00f68c2e08b941f081002fd3691d86a7/8dcc1f1915b241b3a10c8e5b8a76b062.html</t>
-        </is>
-      </c>
-      <c r="I73" s="2" t="inlineStr">
-        <is>
-          <t>Completado desde el enlace Initial Setup.</t>
-        </is>
-      </c>
-      <c r="J73" s="2" t="inlineStr"/>
-      <c r="K73" s="2" t="inlineStr"/>
-      <c r="L73" s="2" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>Translation Support</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>J48</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>No disponible</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>No existe enlace de Initial Setup en la sección Resources</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>No existe enlace de Initial Setup en la sección Resources</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t>No existe enlace de Initial Setup en la sección Resources</t>
-        </is>
-      </c>
-      <c r="G74" s="2" t="inlineStr">
-        <is>
-          <t>No aplica</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>No existe enlace de Initial Setup en la sección Resources</t>
-        </is>
-      </c>
-      <c r="I74" s="2" t="inlineStr"/>
-      <c r="J74" s="2" t="inlineStr">
-        <is>
-          <t>SAP LeanIX solutions</t>
-        </is>
-      </c>
-      <c r="K74" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/6719d6d7-fda7-4ea9-b0dd-43b99fbab6b6/</t>
-        </is>
-      </c>
-      <c r="L74" s="2" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>Central Governance</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>J535</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>Configuración técnica</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>Plataforma SAP BTP con global account, subaccounts y entitlements configurados; usuarios onboarded; trust configurado hacia el Identity Authentication tenant y atributos de usuario para Joule definidos. Versión mínima SAP S/4HANA 2023 FPS0.</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>Determinar la vía aplicable según el Initial Setup de Joule: (a) Joule ya disponible; (b) plataforma BTP lista → ejecutar el Joule Booster; o (c) configurar primero la plataforma BTP y luego onboard de Joule. Configurar Trust al tenant de Identity Authentication y los atributos de usuario para Joule antes de ejecutar el Joule Booster; ejecutar el Joule Booster y configurar los dominios de confianza, siguiendo el Joule Onboarding Guide.</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>Validar el acceso de los usuarios a Joule y comprobar que la capability de Central Governance quede disponible en SAP Master Data Governance.</t>
-        </is>
-      </c>
-      <c r="G75" s="2" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="H75" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/joule/integrating-joule-with-sap/initial-setup?version=CLOUD</t>
-        </is>
-      </c>
-      <c r="I75" s="2" t="inlineStr"/>
-      <c r="J75" s="2" t="inlineStr">
-        <is>
-          <t>SAP S/4HANA Cloud for master data governance, private edition</t>
-        </is>
-      </c>
-      <c r="K75" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/a0399e7f-e105-40a9-9169-d63e768735b8/</t>
-        </is>
-      </c>
-      <c r="L75" s="2" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>Joule with SAP S/4HANA Cloud Private Edition</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>J54</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>Activación de Joule con SAP S/4HANA Cloud Private Edition</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t>Joule inicial configurado; SAP S/4HANA Cloud Private Edition compatible; integración con SAP Cloud Identity Services; configuración de usuarios, roles y autorizaciones; preparación de la integración con SAP Build Work Zone/SAP Start si aplica.</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>Completar setup inicial de Joule; seguir la ruta de integración para SAP S/4HANA Cloud Private Edition; configurar confianza, roles y escenarios; habilitar Joule y validar navegación/acciones desde el sistema.</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t>Probar escenarios por línea de negocio, revisar permisos de usuarios finales y usar la misión de Discovery Center de activación para guiar despliegue.</t>
-        </is>
-      </c>
-      <c r="G76" s="2" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/joule/integrating-joule-with-sap/initial-setup</t>
-        </is>
-      </c>
-      <c r="I76" s="2" t="inlineStr"/>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>SAP S/4HANA Cloud Private Edition</t>
-        </is>
-      </c>
-      <c r="K76" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/98ee8608-82bb-49c3-b4ca-805bd6594314/</t>
-        </is>
-      </c>
-      <c r="L76" s="2" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>Joule with SAP Business Technology Platform</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>J57</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>Configuración inicial de Joule / integración de producto SAP</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>Contar con SAP BTP cockpit y subcuenta para Joule; tener la suscripción/entitlement aplicable de Joule; disponer de SAP Cloud Identity Services / Identity Authentication configurado; contar con permisos administrativos para ejecutar el setup e integrar la solución SAP correspondiente.</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t>Revisar prerrequisitos; acceder a SAP BTP cockpit; ejecutar el booster/configuración inicial de Joule cuando aplique; seleccionar la ruta de integración correspondiente; configurar confianza, roles, destinos o formación requerida; activar Joule y validar que el icono/experiencia quede disponible para usuarios autorizados.</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>Validar acceso con usuarios de prueba, revisar permisos y escenarios disponibles, completar la integración específica del producto, comunicar adopción a usuarios y monitorear uso/soporte.</t>
-        </is>
-      </c>
-      <c r="G77" s="2" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/joule/integrating-joule-with-sap/initial-setup</t>
-        </is>
-      </c>
-      <c r="I77" s="2" t="inlineStr"/>
-      <c r="J77" s="2" t="inlineStr">
-        <is>
-          <t>SAP Business Technology Platform</t>
-        </is>
-      </c>
-      <c r="K77" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/9c079680-7938-4ddd-83c4-3d89a7943311/</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>Project Services</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>J586</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>Configuración inicial de Joule para gestión de proyectos</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t>Contar con SAP S/4HANA Cloud Public Edition, suscripción/activación de Joule Base, usuarios con roles de proyecto y permisos para usar capacidades conversacionales de Joule.</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>Verificar que Joule esté habilitado; asignar roles de usuario relevantes; validar acceso a apps de proyectos; probar las consultas o acciones conversacionales para actividades de project services.</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>Monitorear adopción, validar exactitud de respuestas/resúmenes, ajustar roles y capacitar a usuarios de proyecto en prompts y casos de uso soportados.</t>
-        </is>
-      </c>
-      <c r="G78" s="2" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/JOULE</t>
-        </is>
-      </c>
-      <c r="I78" s="2" t="inlineStr"/>
-      <c r="J78" s="2" t="inlineStr">
-        <is>
-          <t>SAP S/4HANA Cloud Public Edition</t>
-        </is>
-      </c>
-      <c r="K78" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/bccabd59-564e-4a4d-84b3-67d6933348cd/</t>
-        </is>
-      </c>
-      <c r="L78" s="2" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>Back Order Processing</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>J597</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>AI Feature</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
-        <is>
-          <t>Joule con SAP S/4HANA Cloud Public Edition, suscripción Joule Base y producto base. Para el proceso BOP funcional, Backorder Processing debe estar configurado en SAP S/4HANA Cloud Public Edition.</t>
-        </is>
-      </c>
-      <c r="E79" s="2" t="inlineStr">
-        <is>
-          <t>Completar integración de Joule con SAP S/4HANA Cloud Public Edition y validar la capacidad de BOP. Funcionalmente, el usuario puede seleccionar/configurar Backorder Processing o usar prompts relevantes para iniciar la interacción.</t>
-        </is>
-      </c>
-      <c r="F79" s="2" t="inlineStr">
-        <is>
-          <t>Probar prompts de BOP y validar que la configuración/ejecución de Back Order Processing responda correctamente dentro del sistema.</t>
-        </is>
-      </c>
-      <c r="G79" s="2" t="inlineStr">
-        <is>
-          <t>Alta: combina configuración de Joule/SAP S/4HANA Cloud Public Edition con conocimiento funcional de BOP/aATP.</t>
-        </is>
-      </c>
-      <c r="H79" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/joule/integrating-joule-with-sap/integration-with-sap-s-4hana-cloud-public-edition</t>
-        </is>
-      </c>
-      <c r="I79" s="2" t="inlineStr"/>
-      <c r="J79" s="2" t="inlineStr"/>
-      <c r="K79" s="2" t="inlineStr"/>
-      <c r="L79" s="2" t="inlineStr">
-        <is>
-          <t>Initial Setup localizado como recurso en Discovery/product page; contenido complementado con guía SAP Help de integración Joule/S/4HANA Cloud Public Edition y ayuda funcional BOP.</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>Joule with SAP Multi-Bank Connectivity</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>J600</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>Joule documental para SAP Multi-Bank Connectivity</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t>Joule Base o entitlement correspondiente; acceso a SAP Multi-Bank Connectivity; permisos para consultar documentación y configurar el producto; usuarios autorizados para usar Joule.</t>
-        </is>
-      </c>
-      <c r="E80" s="2" t="inlineStr">
-        <is>
-          <t>Completar setup inicial de Joule; activar el AI feature desde la página de detalle; validar que Joule pueda responder preguntas sobre SAP Multi-Bank Connectivity con base en SAP Help Portal; revisar documentación de producto.</t>
-        </is>
-      </c>
-      <c r="F80" s="2" t="inlineStr">
-        <is>
-          <t>Probar preguntas frecuentes de documentación, capacitar usuarios de tesorería/conectividad bancaria y revisar controles de seguridad/acceso.</t>
-        </is>
-      </c>
-      <c r="G80" s="2" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="H80" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/joule/integrating-joule-with-sap/initial-setup</t>
-        </is>
-      </c>
-      <c r="I80" s="2" t="inlineStr"/>
-      <c r="J80" s="2" t="inlineStr">
-        <is>
-          <t>SAP Multi-Bank Connectivity</t>
-        </is>
-      </c>
-      <c r="K80" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/5cd6a2a6-c3ba-4bf6-9111-5e2f95757a69/</t>
-        </is>
-      </c>
-      <c r="L80" s="2" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>Anomaly Detection</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>J606</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>AI Feature</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
-        <is>
-          <t>APIs disponibles en SAP Integration Suite/API Management y datos históricos suficientes para entrenar el modelo de anomalías. La documentación remite a los prerrequisitos de selección de APIs.</t>
-        </is>
-      </c>
-      <c r="E81" s="2" t="inlineStr">
-        <is>
-          <t>Configurar o habilitar las APIs seleccionadas para Anomaly Detection desde SAP Integration Suite/API Management siguiendo el procedimiento de 'Configuring APIs for Anomaly Detection'.</t>
-        </is>
-      </c>
-      <c r="F81" s="2" t="inlineStr">
-        <is>
-          <t>Revisar y trabajar con las anomalías detectadas una vez habilitada la detección.</t>
-        </is>
-      </c>
-      <c r="G81" s="2" t="inlineStr">
-        <is>
-          <t>Media: requiere seleccionar APIs válidas y contar con datos históricos suficientes, pero no implica una integración compleja entre varios productos.</t>
-        </is>
-      </c>
-      <c r="H81" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/integration-suite/sap-integration-suite/enabling-apis-for-anomaly-detection</t>
-        </is>
-      </c>
-      <c r="I81" s="2" t="inlineStr"/>
-      <c r="J81" s="2" t="inlineStr"/>
-      <c r="K81" s="2" t="inlineStr"/>
-      <c r="L81" s="2" t="inlineStr">
-        <is>
-          <t>Initial Setup/guía SAP Help localizada para configuración de APIs para Anomaly Detection.</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>Process Generation</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>J638</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>Configuración inicial de generación de procesos</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>Tener SAP Build Process Automation, acceso de desarrollador, tenant con la capacidad de IA disponible y una descripción clara del proceso o automatización requerida.</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>Abrir el entorno de diseño; describir el proceso en lenguaje natural; generar el artefacto inicial; revisar pasos, reglas y lógica; completar ajustes manuales y validar.</t>
-        </is>
-      </c>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t>Probar el flujo generado, documentar supuestos, conectar servicios requeridos y aplicar revisión funcional/técnica antes de pasar a producción.</t>
-        </is>
-      </c>
-      <c r="G82" s="2" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/build-process-automation/sap-build-process-automation/initial-setup</t>
-        </is>
-      </c>
-      <c r="I82" s="2" t="inlineStr"/>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>SAP Build Process Automation</t>
-        </is>
-      </c>
-      <c r="K82" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/50a434ab-f63c-4f3f-a5d2-c661b5d461f2/</t>
-        </is>
-      </c>
-      <c r="L82" s="2" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>Process Editing</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>J639</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>Configuración inicial de IA generativa para automatización</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>Contar con SAP Build Process Automation, roles de desarrollador/configurador, tenant habilitado para capacidades de IA/Joule y artefactos de proceso que puedan editarse.</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr">
-        <is>
-          <t>Asignar roles; abrir el artefacto de proceso; ingresar la instrucción de edición en lenguaje natural; revisar los cambios propuestos; ajustar, validar y guardar o desplegar.</t>
-        </is>
-      </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>Probar los cambios en ambiente de desarrollo, definir controles de revisión y aplicar gobierno sobre modificaciones generadas por IA.</t>
-        </is>
-      </c>
-      <c r="G83" s="2" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/build-process-automation/sap-build-process-automation/initial-setup</t>
-        </is>
-      </c>
-      <c r="I83" s="2" t="inlineStr"/>
-      <c r="J83" s="2" t="inlineStr">
-        <is>
-          <t>SAP Build Process Automation</t>
-        </is>
-      </c>
-      <c r="K83" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/143f1e51-609a-45d9-ab96-bf286e044a03/</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>Process Summarization</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>J640</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>Configuración inicial de resumen de procesos</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>Contar con SAP Build Process Automation, permisos para revisar artefactos y la capacidad de IA disponible para generar resúmenes sobre procesos o automatizaciones existentes.</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="inlineStr">
-        <is>
-          <t>Abrir el artefacto de proceso; ejecutar la opción de resumen asistido; revisar el resumen generado; ajustar la documentación y guardar la versión revisada.</t>
-        </is>
-      </c>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t>Usar el resumen en handovers, revisiones funcionales y documentación; definir controles para asegurar que el resumen represente correctamente el proceso.</t>
-        </is>
-      </c>
-      <c r="G84" s="2" t="inlineStr">
-        <is>
-          <t>Baja-Media</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/build-process-automation/sap-build-process-automation/initial-setup</t>
-        </is>
-      </c>
-      <c r="I84" s="2" t="inlineStr"/>
-      <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t>SAP Build Process Automation</t>
-        </is>
-      </c>
-      <c r="K84" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/69b0874a-e8a6-49e3-b66c-4a6c5b1fd77f/</t>
-        </is>
-      </c>
-      <c r="L84" s="2" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>Form Generation</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>J641</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>AI Feature</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>El enlace de Initial Setup de SAP Help Portal fue identificado para capacidades generativas de SAP Build Process Automation. Para generar un formulario, la documentación relacionada indica como prerequisito tener un proyecto creado.</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
-        <is>
-          <t>Usar la capacidad Generate a Form de SAP Build Process Automation para generar un formulario mediante IA generativa a partir de una descripción. No se agregan pasos adicionales no verificados.</t>
-        </is>
-      </c>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t>No se indican próximos pasos en el enlace consultado.</t>
-        </is>
-      </c>
-      <c r="G85" s="2" t="inlineStr">
-        <is>
-          <t>Media: requiere SAP Build Process Automation y un proyecto existente, pero el uso de la generación de formulario es guiado.</t>
-        </is>
-      </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/build-process-automation/sap-build-process-automation/generate-form</t>
-        </is>
-      </c>
-      <c r="I85" s="2" t="inlineStr"/>
-      <c r="J85" s="2" t="inlineStr"/>
-      <c r="K85" s="2" t="inlineStr"/>
-      <c r="L85" s="2" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>Decision Generation</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>J642</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>AI Feature</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
-        <is>
-          <t>Acceso a SAP Build Process Automation y disponibilidad de las capacidades de IA generativa indicadas en el enlace de Initial Setup. El uso ocurre dentro del diseño de automatizaciones y artefactos de proceso/decisión.</t>
-        </is>
-      </c>
-      <c r="E86" s="2" t="inlineStr">
-        <is>
-          <t>Desde SAP Build Process Automation, usar las capacidades de generative AI descritas en el enlace para generar artefactos de automatización, incluyendo decisiones, a partir de lenguaje natural. El contenido extraído no expone un procedimiento administrativo más detallado.</t>
-        </is>
-      </c>
-      <c r="F86" s="2" t="inlineStr">
-        <is>
-          <t>No se indican próximos pasos en el enlace consultado.</t>
-        </is>
-      </c>
-      <c r="G86" s="2" t="inlineStr">
-        <is>
-          <t>Media: requiere tener disponible SAP Build Process Automation y trabajar con capacidades generativas dentro del diseño de procesos/artefactos, pero no se observa una integración técnica compleja en el texto extraído.</t>
-        </is>
-      </c>
-      <c r="H86" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/build-process-automation/sap-build-process-automation/generative-ai?locale=en-US</t>
-        </is>
-      </c>
-      <c r="I86" s="2" t="inlineStr"/>
-      <c r="J86" s="2" t="inlineStr"/>
-      <c r="K86" s="2" t="inlineStr"/>
-      <c r="L86" s="2" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
-        <is>
-          <t>Decision Summarization</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>J643</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>AI Feature</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
-        <is>
-          <t>Acceso a SAP Build Process Automation y disponibilidad de las capacidades de IA generativa indicadas en el enlace de Initial Setup. La capacidad aplica sobre procesos y artefactos de decisión ya modelados.</t>
-        </is>
-      </c>
-      <c r="E87" s="2" t="inlineStr">
-        <is>
-          <t>Desde SAP Build Process Automation, usar las capacidades de generative AI para generar resúmenes de artefactos complejos o reglas de negocio. El contenido extraído no expone pasos administrativos adicionales.</t>
-        </is>
-      </c>
-      <c r="F87" s="2" t="inlineStr">
-        <is>
-          <t>No se indican próximos pasos en el enlace consultado.</t>
-        </is>
-      </c>
-      <c r="G87" s="2" t="inlineStr">
-        <is>
-          <t>Media: requiere uso de SAP Build Process Automation y comprensión de artefactos de decisión/proceso, pero el procedimiento descrito no muestra configuración avanzada.</t>
-        </is>
-      </c>
-      <c r="H87" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/build-process-automation/sap-build-process-automation/generative-ai?locale=en-US</t>
-        </is>
-      </c>
-      <c r="I87" s="2" t="inlineStr"/>
-      <c r="J87" s="2" t="inlineStr"/>
-      <c r="K87" s="2" t="inlineStr"/>
-      <c r="L87" s="2" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t>Script Task Generation</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>J644</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>Configuración inicial de servicio BTP / SAP Build Process Automation</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
-        <is>
-          <t>Cuenta/subcuenta de SAP BTP con derecho a SAP Build Process Automation; el administrador debe suscribir la subcuenta al servicio y asignar roles/role collections necesarios.</t>
-        </is>
-      </c>
-      <c r="E88" s="2" t="inlineStr">
-        <is>
-          <t>Realizar el setup inicial de SAP Build Process Automation en la subcuenta BTP: suscripción al servicio, configuración de accesos y preparación del entorno para trabajar con procesos y automatizaciones.</t>
-        </is>
-      </c>
-      <c r="F88" s="2" t="inlineStr">
-        <is>
-          <t>Entrar a SAP Build Process Automation, crear o abrir un proyecto de proceso y utilizar la generación de script task dentro del flujo de automatización.</t>
-        </is>
-      </c>
-      <c r="G88" s="2" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/build-process-automation/sap-build-process-automation/initial-setup</t>
-        </is>
-      </c>
-      <c r="I88" s="2" t="inlineStr"/>
-      <c r="J88" s="2" t="inlineStr">
-        <is>
-          <t>SAP Build Process Automation</t>
-        </is>
-      </c>
-      <c r="K88" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/f2310927-98ed-410a-86bb-1ca9ece68e21/</t>
-        </is>
-      </c>
-      <c r="L88" s="2" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t>Booking Agent</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>J650</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>AI Agent</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
-        <is>
-          <t>SAP Concur integrado con Joule, SAP BTP/SAP Build Work Zone e identidad de usuarios según la guía de integración de Joule con SAP Concur. Puede requerir entitlement/autorización adicional.</t>
-        </is>
-      </c>
-      <c r="E89" s="2" t="inlineStr">
-        <is>
-          <t>Seguir la guía 'Integration With SAP Concur' para integrar Joule con SAP Concur: completar configuración de Joule Base, sincronización/provisionamiento de usuarios y validación de acceso a Joule en el contexto de Concur.</t>
-        </is>
-      </c>
-      <c r="F89" s="2" t="inlineStr">
-        <is>
-          <t>Validar el uso del Booking Agent en Concur Travel y que las recomendaciones de viaje cumplan políticas, preferencias y restricciones de presupuesto.</t>
-        </is>
-      </c>
-      <c r="G89" s="2" t="inlineStr">
-        <is>
-          <t>Alta: requiere integración entre SAP Concur, Joule, SAP Build Work Zone/BTP y gestión de usuarios/identidad.</t>
-        </is>
-      </c>
-      <c r="H89" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/joule/integrating-joule-with-sap/integration-with-sap-concur</t>
-        </is>
-      </c>
-      <c r="I89" s="2" t="inlineStr"/>
-      <c r="J89" s="2" t="inlineStr"/>
-      <c r="K89" s="2" t="inlineStr"/>
-      <c r="L89" s="2" t="inlineStr">
-        <is>
-          <t>Guía SAP Help localizada para integración Joule con SAP Concur.</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
-        <is>
-          <t>Architecture Guidance</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>J652</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>AI Feature</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
-        <is>
-          <t>No existe enlace de Initial Setup en la sección Resources confirmado con la información accesible. No se completan prerequisitos con otra fuente.</t>
-        </is>
-      </c>
-      <c r="E90" s="2" t="inlineStr">
-        <is>
-          <t>No existe enlace de Initial Setup en la sección Resources confirmado con la información accesible. No se completa procedimiento con otra fuente.</t>
-        </is>
-      </c>
-      <c r="F90" s="2" t="inlineStr">
-        <is>
-          <t>No existe enlace de Initial Setup en la sección Resources confirmado con la información accesible.</t>
-        </is>
-      </c>
-      <c r="G90" s="2" t="inlineStr">
-        <is>
-          <t>No estimable: no se localizó enlace específico de Initial Setup para esta feature en la información accesible.</t>
-        </is>
-      </c>
-      <c r="H90" s="2" t="inlineStr"/>
-      <c r="I90" s="2" t="inlineStr"/>
-      <c r="J90" s="2" t="inlineStr"/>
-      <c r="K90" s="2" t="inlineStr"/>
-      <c r="L90" s="2" t="inlineStr">
-        <is>
-          <t>Se localizó documentación SAP Help de AI-Assisted Architecture Guidance, pero no un recurso específico 'Initial Setup - SAP Help Portal'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
-        <is>
-          <t>Insights Description Generator</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>J669</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>AI Feature</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>El enlace de Initial Setup aparece en Resources, pero no fue posible acceder a su contenido exacto desde este entorno. No se completa con otra fuente.</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr">
-        <is>
-          <t>El enlace de Initial Setup aparece en Resources, pero no fue posible acceder a su contenido exacto desde este entorno. No se completa con otra fuente.</t>
-        </is>
-      </c>
-      <c r="F91" s="2" t="inlineStr">
-        <is>
-          <t>El enlace de Initial Setup aparece en Resources, pero no fue posible acceder a su contenido exacto desde este entorno. No se completa con otra fuente.</t>
-        </is>
-      </c>
-      <c r="G91" s="2" t="inlineStr">
-        <is>
-          <t>No evaluable con seguridad. No se accedió al contenido exacto del Initial Setup.</t>
-        </is>
-      </c>
-      <c r="H91" s="2" t="inlineStr">
-        <is>
-          <t>No fue posible resolver con seguridad el enlace exacto de Initial Setup desde la página consultada en este entorno.</t>
-        </is>
-      </c>
-      <c r="I91" s="2" t="inlineStr"/>
-      <c r="J91" s="2" t="inlineStr"/>
-      <c r="K91" s="2" t="inlineStr"/>
-      <c r="L91" s="2" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t>Performance Preparation Agent</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>J671</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>Initial Setup identificado en Resources, pero contenido no accesible</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
-        <is>
-          <t>Enlace de Initial Setup identificado en Resources, pero no fue posible resolver o acceder al contenido de SAP Help Portal tras reintentos.</t>
-        </is>
-      </c>
-      <c r="E92" s="2" t="inlineStr">
-        <is>
-          <t>Enlace de Initial Setup identificado en Resources, pero no fue posible resolver o acceder al contenido de SAP Help Portal tras reintentos.</t>
-        </is>
-      </c>
-      <c r="F92" s="2" t="inlineStr">
-        <is>
-          <t>Enlace de Initial Setup identificado en Resources, pero no fue posible resolver o acceder al contenido de SAP Help Portal tras reintentos.</t>
-        </is>
-      </c>
-      <c r="G92" s="2" t="inlineStr">
-        <is>
-          <t>No determinada por inaccesibilidad del enlace</t>
-        </is>
-      </c>
-      <c r="H92" s="2" t="inlineStr">
-        <is>
-          <t>Enlace de Initial Setup identificado en Resources, pero no fue posible resolver o acceder al contenido de SAP Help Portal tras reintentos.</t>
-        </is>
-      </c>
-      <c r="I92" s="2" t="inlineStr"/>
-      <c r="J92" s="2" t="inlineStr"/>
-      <c r="K92" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/761a2305-b0a2-4262-b9a3-abd4945ad314/</t>
-        </is>
-      </c>
-      <c r="L92" s="2" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
-        <is>
-          <t>Joule with SAP S/4HANA Cloud Public Edition</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>J74</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>Activación de Joule con SAP S/4HANA Cloud Public Edition</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
-        <is>
-          <t>Joule inicial configurado; tenant de SAP S/4HANA Cloud Public Edition; SAP Cloud Identity Services; roles/autorizaciones para usuarios; preparación de Application Clients e integración BTP según ruta de setup.</t>
-        </is>
-      </c>
-      <c r="E93" s="2" t="inlineStr">
-        <is>
-          <t>Completar setup inicial de Joule; activar la integración con SAP S/4HANA Cloud Public Edition; configurar identidad, clientes/aplicaciones y permisos; validar que Joule responda y navegue dentro del ERP Cloud Public.</t>
-        </is>
-      </c>
-      <c r="F93" s="2" t="inlineStr">
-        <is>
-          <t>Probar casos de datos de negocio, navegación y tareas transaccionales; revisar adopción de usuarios y documentación de escenarios disponibles.</t>
-        </is>
-      </c>
-      <c r="G93" s="2" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="H93" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/joule/integrating-joule-with-sap/initial-setup</t>
-        </is>
-      </c>
-      <c r="I93" s="2" t="inlineStr"/>
-      <c r="J93" s="2" t="inlineStr">
-        <is>
-          <t>SAP S/4HANA Cloud Public Edition</t>
-        </is>
-      </c>
-      <c r="K93" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/59d61974-9d59-4e32-9026-189462bbf54f/</t>
-        </is>
-      </c>
-      <c r="L93" s="2" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>Supplier Delivery Date Mass Update</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>J757</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>No disponible</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
-        <is>
-          <t>No existe enlace de Initial Setup en la sección Resources</t>
-        </is>
-      </c>
-      <c r="E94" s="2" t="inlineStr">
-        <is>
-          <t>No existe enlace de Initial Setup en la sección Resources</t>
-        </is>
-      </c>
-      <c r="F94" s="2" t="inlineStr">
-        <is>
-          <t>No existe enlace de Initial Setup en la sección Resources</t>
-        </is>
-      </c>
-      <c r="G94" s="2" t="inlineStr">
-        <is>
-          <t>No aplica</t>
-        </is>
-      </c>
-      <c r="H94" s="2" t="inlineStr">
-        <is>
-          <t>No existe enlace de Initial Setup en la sección Resources</t>
-        </is>
-      </c>
-      <c r="I94" s="2" t="inlineStr"/>
-      <c r="J94" s="2" t="inlineStr">
-        <is>
-          <t>SAP S/4HANA Cloud Public Edition</t>
-        </is>
-      </c>
-      <c r="K94" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/d7b65dad-4fa1-4430-a860-6c8eba5ff8e1/</t>
-        </is>
-      </c>
-      <c r="L94" s="2" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
-        <is>
-          <t>Joule and Microsoft 365 Copilot</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>J762</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>Integración Joule con Microsoft 365 Copilot</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
-        <is>
-          <t>Joule ya activado en el landscape SAP; entorno Microsoft 365 Copilot licenciado; alineación de identidad entre SAP y Microsoft; configuración de red/confianza para comunicación segura entre plataformas.</t>
-        </is>
-      </c>
-      <c r="E95" s="2" t="inlineStr">
-        <is>
-          <t>Completar setup inicial de Joule; activar explícitamente la integración con Microsoft 365 Copilot; configurar identidad y autorización; validar uso desde Microsoft Teams/Copilot y desde Joule.</t>
-        </is>
-      </c>
-      <c r="F95" s="2" t="inlineStr">
-        <is>
-          <t>Probar consultas cruzadas SAP–Microsoft 365, verificar transparencia de respuestas y permisos, y usar la misión de Discovery Center para guiar la activación productiva.</t>
-        </is>
-      </c>
-      <c r="G95" s="2" t="inlineStr">
-        <is>
-          <t>Media-Alta</t>
-        </is>
-      </c>
-      <c r="H95" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/joule/integrating-joule-with-sap/initial-setup</t>
-        </is>
-      </c>
-      <c r="I95" s="2" t="inlineStr"/>
-      <c r="J95" s="2" t="inlineStr">
-        <is>
-          <t>Joule</t>
-        </is>
-      </c>
-      <c r="K95" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/4dfa3fea-c5d2-40e3-959d-317b07b6b64e/</t>
-        </is>
-      </c>
-      <c r="L95" s="2" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
-        <is>
-          <t>Behavioral Insights for Contract Accounting</t>
-        </is>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>J765</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>AI Feature</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
-        <is>
-          <t>El enlace de Initial Setup existe en la sección Resources. No fue posible extraer contenido textual completo con el extractor desde ese enlace específico. No se completan prerequisitos con otra fuente.</t>
-        </is>
-      </c>
-      <c r="E96" s="2" t="inlineStr">
-        <is>
-          <t>El enlace de Initial Setup existe, pero el contenido textual completo no fue extraíble desde el enlace específico con las herramientas disponibles. No se completa procedimiento con otra fuente.</t>
-        </is>
-      </c>
-      <c r="F96" s="2" t="inlineStr">
-        <is>
-          <t>El enlace de Initial Setup existe, pero no se extrajeron próximos pasos del contenido.</t>
-        </is>
-      </c>
-      <c r="G96" s="2" t="inlineStr">
-        <is>
-          <t>No estimable con rigor: el enlace existe, pero no se pudo extraer el procedimiento completo desde el contenido.</t>
-        </is>
-      </c>
-      <c r="H96" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/SAP_S4HANA_ON-PREMISE/8308e6d301d54584a33cd04a9861bc52/ebf9f8b183934975b07b0c0ff2484b84.html?version=2023.002</t>
-        </is>
-      </c>
-      <c r="I96" s="2" t="inlineStr"/>
-      <c r="J96" s="2" t="inlineStr"/>
-      <c r="K96" s="2" t="inlineStr"/>
-      <c r="L96" s="2" t="inlineStr">
-        <is>
-          <t>Initial Setup existe en Resources y se resolvió a SAP Help, pero el extractor devolvió contenido vacío; se evita rellenar con información externa.</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
-        <is>
-          <t>Retrieval of Equipment Information in Service Management</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>J777</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>Configuración de Joule/IA para service management</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
-        <is>
-          <t>Contar con SAP S/4HANA Cloud Private Edition, datos de equipos instalados, historial de transacciones de servicio, garantías y Joule/capacidad de IA habilitada para service management.</t>
-        </is>
-      </c>
-      <c r="E97" s="2" t="inlineStr">
-        <is>
-          <t>Verificar datos maestros e historial de equipo; asignar roles de service manager; habilitar la capacidad de recuperación/resumen de información; probar consultas sobre equipo, garantía e historial de servicio.</t>
-        </is>
-      </c>
-      <c r="F97" s="2" t="inlineStr">
-        <is>
-          <t>Validar recomendaciones con equipos de servicio, monitorear calidad de respuestas y asegurar gobierno de datos de equipo y transacciones históricas.</t>
-        </is>
-      </c>
-      <c r="G97" s="2" t="inlineStr">
-        <is>
-          <t>Media-Alta</t>
-        </is>
-      </c>
-      <c r="H97" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/JOULE</t>
-        </is>
-      </c>
-      <c r="I97" s="2" t="inlineStr"/>
-      <c r="J97" s="2" t="inlineStr">
-        <is>
-          <t>SAP S/4HANA Cloud Private Edition</t>
-        </is>
-      </c>
-      <c r="K97" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/3de36a16-73ca-4df6-94d2-ccd0dc806192/</t>
-        </is>
-      </c>
-      <c r="L97" s="2" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
-        <is>
-          <t>Requirement Generation</t>
-        </is>
-      </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>J778</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>Configuración funcional de generación de requerimientos</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
-        <is>
-          <t>Tener SAP Cloud ALM disponible, acceso a la app Documents/Requirements y documentos o notas de workshop que puedan utilizarse para generar requerimientos.</t>
-        </is>
-      </c>
-      <c r="E98" s="2" t="inlineStr">
-        <is>
-          <t>Crear o seleccionar un documento en SAP Cloud ALM; usar la opción de generación asistida por IA; revisar los requerimientos sugeridos; ajustar contenido y aprobar/guardar los resultados.</t>
-        </is>
-      </c>
-      <c r="F98" s="2" t="inlineStr">
-        <is>
-          <t>Validar requerimientos con consultores funcionales, relacionarlos con tareas o procesos Fit-to-Standard y definir controles de calidad sobre los requisitos generados.</t>
-        </is>
-      </c>
-      <c r="G98" s="2" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="H98" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/cloud-alm/applicationhelp/ai-assisted-requirement-generation</t>
-        </is>
-      </c>
-      <c r="I98" s="2" t="inlineStr"/>
-      <c r="J98" s="2" t="inlineStr">
-        <is>
-          <t>SAP Cloud ALM</t>
-        </is>
-      </c>
-      <c r="K98" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/e5701d25-2615-49ad-acf3-4f2a6363a206/</t>
-        </is>
-      </c>
-      <c r="L98" s="2" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
-        <is>
-          <t>SAP Joule for Developers‚ ABAP AI capabilities</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>J792</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>Configuración de Joule for Developers ABAP en S/4HANA Cloud Public Edition</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>Contar con SAP S/4HANA Cloud Public Edition, usuario desarrollador y habilitación de Joule for Developers con ABAP AI capabilities.</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
-        <is>
-          <t>Validar disponibilidad del entitlement; suscribirse o habilitar la capacidad; configurar acceso de desarrolladores y probar las capacidades ABAP AI desde las herramientas soportadas.</t>
-        </is>
-      </c>
-      <c r="F99" s="2" t="inlineStr">
-        <is>
-          <t>Capacitar desarrolladores, validar calidad del código generado y establecer controles de revisión antes de transporte o despliegue.</t>
-        </is>
-      </c>
-      <c r="G99" s="2" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="H99" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/abap-ai/generative-ai-in-abap-cloud/subscribing-to-joule-for-developers-abap-ai-capabilities</t>
-        </is>
-      </c>
-      <c r="I99" s="2" t="inlineStr"/>
-      <c r="J99" s="2" t="inlineStr">
-        <is>
-          <t>SAP S/4HANA Cloud Public Edition</t>
-        </is>
-      </c>
-      <c r="K99" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/3c06a28b-576b-47ba-a2be-de0588391d6a/</t>
-        </is>
-      </c>
-      <c r="L99" s="2" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
-        <is>
-          <t>Supplier Delivery Date Prediction</t>
-        </is>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>J811</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>Initial Setup inaccesible desde Resources</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
-        <is>
-          <t>Enlace de Initial Setup identificado en Resources, pero no fue posible acceder o recuperar la URL final desde la página dinámica tras reintentos.</t>
-        </is>
-      </c>
-      <c r="E100" s="2" t="inlineStr">
-        <is>
-          <t>Enlace de Initial Setup identificado en Resources, pero no fue posible acceder o recuperar la URL final desde la página dinámica tras reintentos.</t>
-        </is>
-      </c>
-      <c r="F100" s="2" t="inlineStr">
-        <is>
-          <t>Enlace de Initial Setup identificado en Resources, pero no fue posible acceder o recuperar la URL final desde la página dinámica tras reintentos.</t>
-        </is>
-      </c>
-      <c r="G100" s="2" t="inlineStr">
-        <is>
-          <t>No determinada</t>
-        </is>
-      </c>
-      <c r="H100" s="2" t="inlineStr">
-        <is>
-          <t>Enlace de Initial Setup identificado en Resources, pero no fue posible acceder o recuperar la URL final desde la página dinámica tras reintentos.</t>
-        </is>
-      </c>
-      <c r="I100" s="2" t="inlineStr"/>
-      <c r="J100" s="2" t="inlineStr">
-        <is>
-          <t>SAP S/4HANA Cloud Private Edition</t>
-        </is>
-      </c>
-      <c r="K100" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/c264b09d-42ca-4256-8d8e-0da5af6c838a/</t>
-        </is>
-      </c>
-      <c r="L100" s="2" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
-        <is>
-          <t>Resolution of Implausible Meter Readings</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>J824</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>Configuración técnica/funcional de machine learning en IS-U</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
-        <is>
-          <t>Contar con SAP S/4HANA Cloud Private Edition para Utilities/IS-U, datos históricos de lecturas, autorizaciones sobre documentos de lectura de medidor y modelo/escenario de machine learning entrenado y activado.</t>
-        </is>
-      </c>
-      <c r="E101" s="2" t="inlineStr">
-        <is>
-          <t>Preparar datos históricos; ejecutar la determinación de características de consumo; entrenar/activar el modelo; ejecutar el cálculo de confidence para lecturas implausibles; revisar resultados en la app correspondiente.</t>
-        </is>
-      </c>
-      <c r="F101" s="2" t="inlineStr">
-        <is>
-          <t>Monitorear la calidad de recomendaciones, ajustar umbrales de liberación automática y reentrenar el modelo con datos actualizados.</t>
-        </is>
-      </c>
-      <c r="G101" s="2" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="H101" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/SAP_S4HANA_ON-PREMISE/021b182b0c47416c8fafed67ebfd78a9/b851f6579d3ebd12e10000000a4450e5.html</t>
-        </is>
-      </c>
-      <c r="I101" s="2" t="inlineStr"/>
-      <c r="J101" s="2" t="inlineStr">
-        <is>
-          <t>SAP S/4HANA Cloud Private Edition</t>
-        </is>
-      </c>
-      <c r="K101" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/4d67f2b1-6f72-4c6f-bce3-e6d4c0e89b1c/</t>
-        </is>
-      </c>
-      <c r="L101" s="2" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t>Resolution of Outsorted Billing Documents</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>J825</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>Configuración técnica/funcional de machine learning en billing IS-U</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
-        <is>
-          <t>Contar con SAP S/4HANA Cloud Private Edition para Utilities/IS-U, procesos de billing activos, datos de documentos outsorted y autorizaciones para analizar y procesar documentos de facturación.</t>
-        </is>
-      </c>
-      <c r="E102" s="2" t="inlineStr">
-        <is>
-          <t>Validar los datos y autorizaciones; configurar/activar el escenario de machine learning aplicable; procesar documentos outsorted desde la app de resolución; revisar recomendaciones y resultados de excepción.</t>
-        </is>
-      </c>
-      <c r="F102" s="2" t="inlineStr">
-        <is>
-          <t>Ajustar reglas de excepción, monitorear eficiencia del especialista de facturación y revisar periódicamente calidad de recomendaciones.</t>
-        </is>
-      </c>
-      <c r="G102" s="2" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="H102" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/SAP_S4HANA_ON-PREMISE/021b182b0c47416c8fafed67ebfd78a9/e668f657772ebc12e10000000a4450e5.html</t>
-        </is>
-      </c>
-      <c r="I102" s="2" t="inlineStr"/>
-      <c r="J102" s="2" t="inlineStr">
-        <is>
-          <t>SAP S/4HANA Cloud Private Edition</t>
-        </is>
-      </c>
-      <c r="K102" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/f9a4201e-955f-4aaf-b41a-d2479fb13ed1/</t>
-        </is>
-      </c>
-      <c r="L102" s="2" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
-        <is>
-          <t>Sales Order Creation</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>J831</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>Configuración de Document AI para creación de órdenes de venta</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
-        <is>
-          <t>Contar con SAP S/4HANA Cloud Public Edition, permisos para creación de órdenes de venta, SAP Document AI/AI-assisted extraction habilitado y documentos de compra no estructurados soportados.</t>
-        </is>
-      </c>
-      <c r="E103" s="2" t="inlineStr">
-        <is>
-          <t>Cargar el archivo PDF o imagen; dejar que el sistema extraiga datos; revisar la solicitud de orden; validar sold-to party y campos propuestos; corregir y convertir en orden de venta.</t>
-        </is>
-      </c>
-      <c r="F103" s="2" t="inlineStr">
-        <is>
-          <t>Medir tasa de error, usar revisión de extracciones cuando aplique y mantener control sobre documentos que requieren corrección manual.</t>
-        </is>
-      </c>
-      <c r="G103" s="2" t="inlineStr">
-        <is>
-          <t>Media-Alta</t>
-        </is>
-      </c>
-      <c r="H103" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/SAP_S4HANA_CLOUD/ee9ee0ca4c3942068ea584d2f929b5b1/8fb6388831014cbaaab0df5192c89000.html</t>
-        </is>
-      </c>
-      <c r="I103" s="2" t="inlineStr"/>
-      <c r="J103" s="2" t="inlineStr">
-        <is>
-          <t>SAP S/4HANA Cloud Public Edition</t>
-        </is>
-      </c>
-      <c r="K103" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/5d3d1312-92d7-478a-8e95-f0f0130f5666/</t>
-        </is>
-      </c>
-      <c r="L103" s="2" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
-        <is>
-          <t>Sales Order Creation</t>
-        </is>
-      </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>J832</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>Configuración funcional de creación automática de pedidos de venta</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
-        <is>
-          <t>Contar con SAP S/4HANA Cloud Private Edition, habilitación de la funcionalidad de creación de pedidos desde datos no estructurados y acceso de usuarios internos de ventas a las apps correspondientes.</t>
-        </is>
-      </c>
-      <c r="E104" s="2" t="inlineStr">
-        <is>
-          <t>Validar que la capacidad esté habilitada; preparar el proceso de carga de archivos PDF o imagen; revisar que la extracción automática genere solicitudes de pedido con valores propuestos; probar la conversión posterior a pedido de venta.</t>
-        </is>
-      </c>
-      <c r="F104" s="2" t="inlineStr">
-        <is>
-          <t>Revisar calidad de extracción, entrenar a usuarios de ventas, ajustar validaciones de datos maestros y monitorear errores recurrentes en solicitudes de pedido.</t>
-        </is>
-      </c>
-      <c r="G104" s="2" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="H104" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/SAP_BUILD_PROCESS_AUTOMATION_DESKTOP_AGENT/eae9c11a17a14cfc93e08b22e8574305/145b77281a084a64ae03685a087ca84b.html</t>
-        </is>
-      </c>
-      <c r="I104" s="2" t="inlineStr"/>
-      <c r="J104" s="2" t="inlineStr">
-        <is>
-          <t>SAP S/4HANA Cloud Private Edition</t>
-        </is>
-      </c>
-      <c r="K104" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/836b7ca4-0177-4757-8152-51846c586f1e/</t>
-        </is>
-      </c>
-      <c r="L104" s="2" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
-        <is>
-          <t>Sales Order Creation</t>
-        </is>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>J846</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>Configuración de extracción documental para ventas</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
-        <is>
-          <t>Contar con SAP S/4HANA, SAP Document AI o capacidad equivalente de extracción habilitada, permisos para crear solicitudes/órdenes de venta y documentos de compra en PDF o imagen.</t>
-        </is>
-      </c>
-      <c r="E105" s="2" t="inlineStr">
-        <is>
-          <t>Preparar los documentos de entrada; cargar el archivo; revisar extracción automática; completar/corregir campos sugeridos; convertir la solicitud en orden de venta cuando proceda.</t>
-        </is>
-      </c>
-      <c r="F105" s="2" t="inlineStr">
-        <is>
-          <t>Revisar errores de extracción, ajustar aprendizaje/validación y definir criterios de aceptación antes de contabilizar o convertir documentos.</t>
-        </is>
-      </c>
-      <c r="G105" s="2" t="inlineStr">
-        <is>
-          <t>Media-Alta</t>
-        </is>
-      </c>
-      <c r="H105" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/SAP_S4HANA_CLOUD/ee9ee0ca4c3942068ea584d2f929b5b1/8fb6388831014cbaaab0df5192c89000.html</t>
-        </is>
-      </c>
-      <c r="I105" s="2" t="inlineStr"/>
-      <c r="J105" s="2" t="inlineStr">
-        <is>
-          <t>SAP S/4HANA</t>
-        </is>
-      </c>
-      <c r="K105" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/451531fc-438b-4ecd-a3be-3efb74cb99f5/</t>
-        </is>
-      </c>
-      <c r="L105" s="2" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t>Supplier Delivery Date Prediction</t>
-        </is>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>J848</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>Initial Setup inaccesible desde Resources</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
-        <is>
-          <t>Enlace de Initial Setup identificado en Resources, pero no fue posible acceder o recuperar la URL final desde la página dinámica tras reintentos.</t>
-        </is>
-      </c>
-      <c r="E106" s="2" t="inlineStr">
-        <is>
-          <t>Enlace de Initial Setup identificado en Resources, pero no fue posible acceder o recuperar la URL final desde la página dinámica tras reintentos.</t>
-        </is>
-      </c>
-      <c r="F106" s="2" t="inlineStr">
-        <is>
-          <t>Enlace de Initial Setup identificado en Resources, pero no fue posible acceder o recuperar la URL final desde la página dinámica tras reintentos.</t>
-        </is>
-      </c>
-      <c r="G106" s="2" t="inlineStr">
-        <is>
-          <t>No determinada</t>
-        </is>
-      </c>
-      <c r="H106" s="2" t="inlineStr">
-        <is>
-          <t>Enlace de Initial Setup identificado en Resources, pero no fue posible acceder o recuperar la URL final desde la página dinámica tras reintentos.</t>
-        </is>
-      </c>
-      <c r="I106" s="2" t="inlineStr"/>
-      <c r="J106" s="2" t="inlineStr">
-        <is>
-          <t>SAP S/4HANA</t>
-        </is>
-      </c>
-      <c r="K106" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/e0dd79ff-4ed9-4d79-9461-2be67e664a3c/</t>
-        </is>
-      </c>
-      <c r="L106" s="2" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
-        <is>
-          <t>Joule with Regulatory Change Manager</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>J85</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>Setup de producto + habilitación Joule</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
-        <is>
-          <t>Tener acceso a Regulatory Change Manager; usuarios y roles adecuados para administrar cambios regulatorios y usar Joule; consentimiento/configuración inicial requerida por el producto.</t>
-        </is>
-      </c>
-      <c r="E107" s="2" t="inlineStr">
-        <is>
-          <t>Validar roles en Regulatory Change Manager; completar la configuración inicial indicada en SAP Help Portal; habilitar o revisar el acceso de Joule y los permisos de usuarios; validar búsqueda y evaluación de cambios regulatorios.</t>
-        </is>
-      </c>
-      <c r="F107" s="2" t="inlineStr">
-        <is>
-          <t>Definir responsables de seguimiento regulatorio, validar flujos de revisión/impacto y monitorear resultados de búsqueda de Joule.</t>
-        </is>
-      </c>
-      <c r="G107" s="2" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="H107" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/REGULATORY_CHANGE_MANAGER</t>
-        </is>
-      </c>
-      <c r="I107" s="2" t="inlineStr"/>
-      <c r="J107" s="2" t="inlineStr">
-        <is>
-          <t>Regulatory Change Manager</t>
-        </is>
-      </c>
-      <c r="K107" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/90b39e72-5dd5-4ae1-aef1-840c6e1ff6b2/</t>
-        </is>
-      </c>
-      <c r="L107" s="2" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
-        <is>
-          <t>Explanation of Fixed Asset Depreciation Keys</t>
-        </is>
-      </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>J86</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>AI Feature</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
-        <is>
-          <t>El enlace de Initial Setup existe en Resources. El enlace de SAP Help Portal corresponde a AI-Generated Explanation of Depreciation Keys; el contenido completo de prerequisitos no fue totalmente extractable, por lo que no se agregan dependencias no verificadas.</t>
-        </is>
-      </c>
-      <c r="E108" s="2" t="inlineStr">
-        <is>
-          <t>Consultar la página de SAP Help Portal de AI-Generated Explanation of Depreciation Keys. No se agregan pasos adicionales no verificados.</t>
-        </is>
-      </c>
-      <c r="F108" s="2" t="inlineStr">
-        <is>
-          <t>No se indican próximos pasos en el enlace consultado.</t>
-        </is>
-      </c>
-      <c r="G108" s="2" t="inlineStr">
-        <is>
-          <t>Media: requiere configuración/uso dentro de SAP S/4HANA Cloud Public Edition y acceso a la funcionalidad de activos fijos.</t>
-        </is>
-      </c>
-      <c r="H108" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/SAP_S4HANA_CLOUD/ee9ee0ca4c3942068ea584d2f929b5b1/17fe86dc95334287b50406d466a26c14.html</t>
-        </is>
-      </c>
-      <c r="I108" s="2" t="inlineStr"/>
-      <c r="J108" s="2" t="inlineStr"/>
-      <c r="K108" s="2" t="inlineStr"/>
-      <c r="L108" s="2" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
-        <is>
-          <t>Analytical Business Insights</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>J88</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>AI Feature</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
-        <is>
-          <t>El enlace de SAP Help consultado para AI-Assisted Analytical Business Insights referencia configuración relacionada con Intelligent Scenario Lifecycle Management, acceso a Intelligent Scenario Apps, Generative AI for ISLM, descarga de certificado y creación de SAP BTP Service Instance and Key.</t>
-        </is>
-      </c>
-      <c r="E109" s="2" t="inlineStr">
-        <is>
-          <t>Realizar el setup inicial del escenario siguiendo las secciones de SAP Help: acceder a las Intelligent Scenario Apps, configurar Generative AI for ISLM, descargar el certificado y crear la instancia/clave de servicio SAP BTP requerida.</t>
-        </is>
-      </c>
-      <c r="F109" s="2" t="inlineStr">
-        <is>
-          <t>No se indican próximos pasos en el enlace consultado.</t>
-        </is>
-      </c>
-      <c r="G109" s="2" t="inlineStr">
-        <is>
-          <t>Alta: involucra ISLM, certificado y creación de service instance/key en SAP BTP.</t>
-        </is>
-      </c>
-      <c r="H109" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/SAP_S4HANA_CLOUD/a630d57fc5004c6383e7a81efee7a8bb/f28304dcfa8c4104a137eb82c75c2ef2.html</t>
-        </is>
-      </c>
-      <c r="I109" s="2" t="inlineStr"/>
-      <c r="J109" s="2" t="inlineStr"/>
-      <c r="K109" s="2" t="inlineStr"/>
-      <c r="L109" s="2" t="inlineStr">
-        <is>
-          <t>Initial Setup accesible/resuelto; el extractor no devuelve líneas completas, pero la búsqueda SAP Help indexa secciones relevantes del mismo enlace.</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
-        <is>
-          <t>Run Forecasts in Time Series or Line Charts</t>
-        </is>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>J885</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>Configuración analítica predictiva en SAP Analytics Cloud</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
-        <is>
-          <t>Contar con SAP Analytics Cloud, una historia con gráfico de serie de tiempo o línea, una dimensión de fecha y medidas con datos históricos suficientes.</t>
-        </is>
-      </c>
-      <c r="E110" s="2" t="inlineStr">
-        <is>
-          <t>Abrir la historia; seleccionar el gráfico compatible; ejecutar el forecast predictivo; revisar horizonte, intervalos y resultados; ajustar configuración si es necesario.</t>
-        </is>
-      </c>
-      <c r="F110" s="2" t="inlineStr">
-        <is>
-          <t>Validar la calidad del forecast con el negocio, actualizar datos históricos y documentar supuestos para decisiones futuras.</t>
-        </is>
-      </c>
-      <c r="G110" s="2" t="inlineStr">
-        <is>
-          <t>Baja-Media</t>
-        </is>
-      </c>
-      <c r="H110" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/SAP_ANALYTICS_CLOUD/00f68c2e08b941f081002fd3691d86a7/8f9665dcf53f4f3f90e920995cdd5f05.html</t>
-        </is>
-      </c>
-      <c r="I110" s="2" t="inlineStr"/>
-      <c r="J110" s="2" t="inlineStr">
-        <is>
-          <t>SAP Analytics Cloud</t>
-        </is>
-      </c>
-      <c r="K110" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/6ddc1967-60b4-4d85-b50e-121f4589d27e/</t>
-        </is>
-      </c>
-      <c r="L110" s="2" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
-        <is>
-          <t>Smart Insights</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>J886</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>Configuración inicial de SAP Analytics Cloud</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
-        <is>
-          <t>Tenant de SAP Analytics Cloud, modelo de datos disponible y permisos de usuario para consumir/analizar historias.</t>
-        </is>
-      </c>
-      <c r="E111" s="2" t="inlineStr">
-        <is>
-          <t>Completar la configuración inicial de SAP Analytics Cloud, preparar historias/modelos y asegurar permisos para utilizar capacidades inteligentes.</t>
-        </is>
-      </c>
-      <c r="F111" s="2" t="inlineStr">
-        <is>
-          <t>Usar Smart Insights sobre puntos de datos o desviaciones para obtener explicaciones textuales y visuales.</t>
-        </is>
-      </c>
-      <c r="G111" s="2" t="inlineStr">
-        <is>
-          <t>Baja-Media</t>
-        </is>
-      </c>
-      <c r="H111" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/SAP_ANALYTICS_CLOUD/00f68c2e08b941f081002fd3691d86a7/8b9038ca44f547bf8e69b04e5c55eb37.html</t>
-        </is>
-      </c>
-      <c r="I111" s="2" t="inlineStr"/>
-      <c r="J111" s="2" t="inlineStr">
-        <is>
-          <t>SAP Analytics Cloud</t>
-        </is>
-      </c>
-      <c r="K111" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/9ff17406-6da6-4066-bbb7-2edb8d898dbd/</t>
-        </is>
-      </c>
-      <c r="L111" s="2" t="inlineStr"/>
-    </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
-        <is>
-          <t>Configuration for US Tax Jurisdictions</t>
-        </is>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>J89</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>Configuración administrativa</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
-        <is>
-          <t>Usuario configurado según el tópico 'Enabling AI-Assisted US Tax Jurisdiction Configuration'. Versión de país/región Estados Unidos activada en Manage Your Solution de SAP S/4HANA Cloud Public Edition.</t>
-        </is>
-      </c>
-      <c r="E112" s="2" t="inlineStr">
-        <is>
-          <t>Abrir la actividad de configuración Upload Tax Rates (100426): en la app Manage Your Solution, fijar la versión de país/región en United States y abrir Configure Your Solution; buscar 100426 (o navegar a Finance → Statutory Reporting → Tax). En la pestaña Quick Config, ingresar la dirección o ZIP en el campo Address; la IA devuelve la información de jurisdiction (niveles state, county y ZIP) para revisar. Verificar la ubicación, ingresar manualmente las tasas y las fechas de validez por nivel y, opcionalmente, los campos District y District Jurisdiction; seleccionar Configure para guardar.</t>
-        </is>
-      </c>
-      <c r="F112" s="2" t="inlineStr">
-        <is>
-          <t>Mantener las tasas por cada tax code; verificar el contenido generado por IA contra la autoridad fiscal correspondiente.</t>
-        </is>
-      </c>
-      <c r="G112" s="2" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="H112" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/SAP_S4HANA_CLOUD/fd8427fa19d140c7b66d8457a70473a1/eecd222f00914c058e3268c8aed1f112.html</t>
-        </is>
-      </c>
-      <c r="I112" s="2" t="inlineStr"/>
-      <c r="J112" s="2" t="inlineStr">
-        <is>
-          <t>SAP S/4HANA Cloud Public Edition</t>
-        </is>
-      </c>
-      <c r="K112" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/e547d658-368e-426f-986e-97e574bfb475/</t>
-        </is>
-      </c>
-      <c r="L112" s="2" t="inlineStr"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
-        <is>
-          <t>Smart Grouping</t>
-        </is>
-      </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>J892</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>Configuración inicial de SAP Analytics Cloud</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
-        <is>
-          <t>Tenant de SAP Analytics Cloud y usuarios con permisos para crear/editar historias, modelos o visualizaciones analíticas.</t>
-        </is>
-      </c>
-      <c r="E113" s="2" t="inlineStr">
-        <is>
-          <t>Completar la configuración inicial de SAP Analytics Cloud y preparar el modelo o historia donde se utilizarán gráficos de dispersión o burbuja.</t>
-        </is>
-      </c>
-      <c r="F113" s="2" t="inlineStr">
-        <is>
-          <t>Aplicar Smart Grouping en visualizaciones compatibles para identificar grupos de puntos similares.</t>
-        </is>
-      </c>
-      <c r="G113" s="2" t="inlineStr">
-        <is>
-          <t>Baja-Media</t>
-        </is>
-      </c>
-      <c r="H113" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/SAP_ANALYTICS_CLOUD/00f68c2e08b941f081002fd3691d86a7/8b9038ca44f547bf8e69b04e5c55eb37.html</t>
-        </is>
-      </c>
-      <c r="I113" s="2" t="inlineStr"/>
-      <c r="J113" s="2" t="inlineStr">
-        <is>
-          <t>SAP Analytics Cloud</t>
-        </is>
-      </c>
-      <c r="K113" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/793c4da0-4886-4ee0-9c53-0bc2c465a624/</t>
-        </is>
-      </c>
-      <c r="L113" s="2" t="inlineStr"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
-        <is>
-          <t>Smart Predict</t>
-        </is>
-      </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>J893</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>Configuración inicial de SAP Analytics Cloud</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
-        <is>
-          <t>Tenant de SAP Analytics Cloud con datos/modelos disponibles y permisos para crear modelos predictivos.</t>
-        </is>
-      </c>
-      <c r="E114" s="2" t="inlineStr">
-        <is>
-          <t>Completar la configuración inicial de SAP Analytics Cloud y preparar las fuentes de datos necesarias para escenarios predictivos.</t>
-        </is>
-      </c>
-      <c r="F114" s="2" t="inlineStr">
-        <is>
-          <t>Crear modelos predictivos en SAP Analytics Cloud y consumir los resultados en análisis o planificación.</t>
-        </is>
-      </c>
-      <c r="G114" s="2" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="H114" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/SAP_ANALYTICS_CLOUD/00f68c2e08b941f081002fd3691d86a7/8b9038ca44f547bf8e69b04e5c55eb37.html</t>
-        </is>
-      </c>
-      <c r="I114" s="2" t="inlineStr"/>
-      <c r="J114" s="2" t="inlineStr">
-        <is>
-          <t>SAP Analytics Cloud</t>
-        </is>
-      </c>
-      <c r="K114" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/3e3dbf93-52e2-4a08-b6f3-58b7396bc445/</t>
-        </is>
-      </c>
-      <c r="L114" s="2" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
-        <is>
-          <t>Predictive Planning</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>J894</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>Configuración inicial analítica/predictiva</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
-        <is>
-          <t>Contar con SAP Analytics Cloud para planificación, datos históricos suficientes en el modelo de planificación y roles/permisos para trabajar con capacidades predictivas.</t>
-        </is>
-      </c>
-      <c r="E115" s="2" t="inlineStr">
-        <is>
-          <t>Validar permisos y modelo de planificación; preparar datos históricos; crear o configurar el escenario predictivo; entrenar el modelo; revisar calidad del forecast; aplicar los resultados a la planificación.</t>
-        </is>
-      </c>
-      <c r="F115" s="2" t="inlineStr">
-        <is>
-          <t>Monitorear precisión, actualizar datos, automatizar refrescos de forecast con acciones de planificación y ajustar el modelo según nuevos ciclos de negocio.</t>
-        </is>
-      </c>
-      <c r="G115" s="2" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="H115" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/SAP_ANALYTICS_CLOUD/18850a0e13944f53aa8a8b7c094ea29e/642d0878a5494657bdaa53eac0edb3e0.html</t>
-        </is>
-      </c>
-      <c r="I115" s="2" t="inlineStr"/>
-      <c r="J115" s="2" t="inlineStr">
-        <is>
-          <t>SAP Analytics Cloud</t>
-        </is>
-      </c>
-      <c r="K115" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/07cbfbe5-5fec-4f2f-9e5b-8a7c2dfd6d74/</t>
-        </is>
-      </c>
-      <c r="L115" s="2" t="inlineStr"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
-        <is>
-          <t>Depreciation Key Explanation</t>
-        </is>
-      </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>J898</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>AI Feature</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
-        <is>
-          <t>El enlace de Initial Setup identificado corresponde a documentación de la explicación generada por IA para claves de depreciación. El texto extraído no expone prerequisitos detallados.</t>
-        </is>
-      </c>
-      <c r="E116" s="2" t="inlineStr">
-        <is>
-          <t>El contenido extraído indica la documentación de la explicación generada por IA para claves de depreciación, pero no expone un procedimiento paso a paso de activación.</t>
-        </is>
-      </c>
-      <c r="F116" s="2" t="inlineStr">
-        <is>
-          <t>No se indican próximos pasos en el enlace consultado.</t>
-        </is>
-      </c>
-      <c r="G116" s="2" t="inlineStr">
-        <is>
-          <t>Media: la activación parece depender de una capacidad de SAP S/4HANA Cloud Private Edition y AI Units, pero el enlace extraído no detalla pasos técnicos.</t>
-        </is>
-      </c>
-      <c r="H116" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/SAP_S4HANA_CLOUD/ee9ee0ca4c3942068ea584d2f929b5b1/17fe86dc95334287b50406d466a26c14.html?q=CC05&amp;version=2508.00</t>
-        </is>
-      </c>
-      <c r="I116" s="2" t="inlineStr"/>
-      <c r="J116" s="2" t="inlineStr"/>
-      <c r="K116" s="2" t="inlineStr"/>
-      <c r="L116" s="2" t="inlineStr"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
-        <is>
-          <t>Smart Summarization</t>
-        </is>
-      </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>J90</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>Autorización y habilitación en SAP S/4HANA Cloud Public Edition</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
-        <is>
-          <t>Sistema SAP S/4HANA Cloud Public Edition; la IAM app SAP Business AI - User Interface Features - Smart Summarization (F7924_SUM_TRAN) debe estar disponible y asignada al rol de negocio.</t>
-        </is>
-      </c>
-      <c r="E117" s="2" t="inlineStr">
-        <is>
-          <t>Abrir Display IAM Apps para verificar la IAM app; luego usar Maintain Business Roles para asignarla al rol de los usuarios que utilizarán la capacidad.</t>
-        </is>
-      </c>
-      <c r="F117" s="2" t="inlineStr">
-        <is>
-          <t>Los usuarios pueden abrir una página de objeto SAP Fiori elements, usar el botón Summarize, seleccionar secciones, revisar/editar el resumen y copiarlo para correo o chat.</t>
-        </is>
-      </c>
-      <c r="G117" s="2" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="H117" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/SAP_S4HANA_CLOUD/4fc8d03390c342da8a60f8ee387bca1a/4a69b2cc611a40c4bf5afb42fa016e0e.html</t>
-        </is>
-      </c>
-      <c r="I117" s="2" t="inlineStr"/>
-      <c r="J117" s="2" t="inlineStr">
-        <is>
-          <t>SAP S/4HANA Cloud Public Edition</t>
-        </is>
-      </c>
-      <c r="K117" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/a66caf9e-90e0-44c3-9f4a-47aa40f6027b/</t>
-        </is>
-      </c>
-      <c r="L117" s="2" t="inlineStr"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
-        <is>
-          <t>Easy Filter</t>
-        </is>
-      </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>J91</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>AI Feature</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
-        <is>
-          <t>Acceso administrativo a SAP Fiori launchpad en el sistema SAP S/4HANA Cloud Public Edition. El enlace contiene secciones de prerequisitos, configuración general y habilitación de la funcionalidad.</t>
-        </is>
-      </c>
-      <c r="E118" s="2" t="inlineStr">
-        <is>
-          <t>Iniciar sesión como administrador en SAP Fiori launchpad del sistema SAP S/4HANA Cloud Public Edition y seguir la configuración indicada para habilitar AI-Assisted Easy Filter.</t>
-        </is>
-      </c>
-      <c r="F118" s="2" t="inlineStr">
-        <is>
-          <t>No se indican próximos pasos en el enlace consultado.</t>
-        </is>
-      </c>
-      <c r="G118" s="2" t="inlineStr">
-        <is>
-          <t>Media: requiere acceso de administrador y configuración de la funcionalidad en SAP S/4HANA Cloud Public Edition.</t>
-        </is>
-      </c>
-      <c r="H118" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/SAP_S4HANA_CLOUD/4fc8d03390c342da8a60f8ee387bca1a/e3410abd11404d87b319cb2d63a50a92.html</t>
-        </is>
-      </c>
-      <c r="I118" s="2" t="inlineStr"/>
-      <c r="J118" s="2" t="inlineStr"/>
-      <c r="K118" s="2" t="inlineStr"/>
-      <c r="L118" s="2" t="inlineStr"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
-        <is>
-          <t>Generation of Integrations</t>
-        </is>
-      </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>J92</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>AI Feature</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
-        <is>
-          <t>La feature de IA “Generation of Integrations” debe estar activada para el tenant de SAP Integration Suite. La capacidad está asociada a SAP Integration Suite enhanced y premium editions.</t>
-        </is>
-      </c>
-      <c r="E119" s="2" t="inlineStr">
-        <is>
-          <t>En SAP Integration Suite, usar la opción de generación de integration flows con asistencia de IA: describir el escenario de integración, proporcionar las entradas requeridas y dejar que el sistema genere el integration flow inicial para revisión y ajuste.</t>
-        </is>
-      </c>
-      <c r="F119" s="2" t="inlineStr">
-        <is>
-          <t>Revisar el integration flow generado, validar conectores y configuración, completar ajustes técnicos y continuar con pruebas/despliegue según el flujo estándar de SAP Integration Suite.</t>
-        </is>
-      </c>
-      <c r="G119" s="2" t="inlineStr">
-        <is>
-          <t>Media. La generación se apoya en IA, pero requiere tenant de SAP Integration Suite, feature activada y validación técnica del flujo generado.</t>
-        </is>
-      </c>
-      <c r="H119" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/integration-suite/sap-integration-suite/generating-integration-flows-with-ai-assistance</t>
-        </is>
-      </c>
-      <c r="I119" s="2" t="inlineStr"/>
-      <c r="J119" s="2" t="inlineStr"/>
-      <c r="K119" s="2" t="inlineStr"/>
-      <c r="L119" s="2" t="inlineStr"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
-        <is>
-          <t>Workspace</t>
-        </is>
-      </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>J924</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>Initial Setup inaccesible desde Resources</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
-        <is>
-          <t>Enlace de Initial Setup identificado en Resources, pero no fue posible acceder o recuperar la URL final desde la página dinámica tras reintentos.</t>
-        </is>
-      </c>
-      <c r="E120" s="2" t="inlineStr">
-        <is>
-          <t>Enlace de Initial Setup identificado en Resources, pero no fue posible acceder o recuperar la URL final desde la página dinámica tras reintentos.</t>
-        </is>
-      </c>
-      <c r="F120" s="2" t="inlineStr">
-        <is>
-          <t>Enlace de Initial Setup identificado en Resources, pero no fue posible acceder o recuperar la URL final desde la página dinámica tras reintentos.</t>
-        </is>
-      </c>
-      <c r="G120" s="2" t="inlineStr">
-        <is>
-          <t>No determinada</t>
-        </is>
-      </c>
-      <c r="H120" s="2" t="inlineStr">
-        <is>
-          <t>Enlace de Initial Setup identificado en Resources, pero no fue posible acceder o recuperar la URL final desde la página dinámica tras reintentos.</t>
-        </is>
-      </c>
-      <c r="I120" s="2" t="inlineStr"/>
-      <c r="J120" s="2" t="inlineStr">
-        <is>
-          <t>SAP Document AI</t>
-        </is>
-      </c>
-      <c r="K120" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/41b32187-96c9-4780-aa15-fc3cdfac1006/</t>
-        </is>
-      </c>
-      <c r="L120" s="2" t="inlineStr"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
-        <is>
-          <t>Managing Supplier Invoices</t>
-        </is>
-      </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>J929</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>No existe enlace de Initial Setup en la sección Resources</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
-        <is>
-          <t>No existe enlace de Initial Setup en la sección Resources</t>
-        </is>
-      </c>
-      <c r="E121" s="2" t="inlineStr">
-        <is>
-          <t>No existe enlace de Initial Setup en la sección Resources</t>
-        </is>
-      </c>
-      <c r="F121" s="2" t="inlineStr">
-        <is>
-          <t>No existe enlace de Initial Setup en la sección Resources</t>
-        </is>
-      </c>
-      <c r="G121" s="2" t="inlineStr">
-        <is>
-          <t>No aplica</t>
-        </is>
-      </c>
-      <c r="H121" s="2" t="inlineStr">
-        <is>
-          <t>No existe enlace de Initial Setup en la sección Resources</t>
-        </is>
-      </c>
-      <c r="I121" s="2" t="inlineStr"/>
-      <c r="J121" s="2" t="inlineStr">
-        <is>
-          <t>SAP S/4HANA Cloud Public Edition</t>
-        </is>
-      </c>
-      <c r="K121" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/1fa927d7-80ce-4b9b-8ea1-8ed95be8b8d3/</t>
-        </is>
-      </c>
-      <c r="L121" s="2" t="inlineStr"/>
-    </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
-        <is>
-          <t>Smart Personalization of My Home for Applications</t>
-        </is>
-      </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>J934</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>Autorización y habilitación en SAP S/4HANA Cloud Public Edition</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
-        <is>
-          <t>Sistema SAP S/4HANA Cloud Public Edition; asignar a los usuarios la IAM app SAP Business AI - My Home - Smart App Finder (F8818_TRAN) o el catálogo equivalente.</t>
-        </is>
-      </c>
-      <c r="E122" s="2" t="inlineStr">
-        <is>
-          <t>Verificar la IAM app en Display IAM Apps, asignarla al rol de negocio en Maintain Business Roles y habilitar el acceso para los usuarios requeridos.</t>
-        </is>
-      </c>
-      <c r="F122" s="2" t="inlineStr">
-        <is>
-          <t>Los usuarios pueden buscar apps en My Home con lenguaje natural desde Add Content, revisar resultados sugeridos y agregarlos a Apps o Insights Tiles.</t>
-        </is>
-      </c>
-      <c r="G122" s="2" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="H122" s="2" t="inlineStr">
-        <is>
-          <t>https://help.sap.com/docs/SAP_S4HANA_CLOUD/4fc8d03390c342da8a60f8ee387bca1a/3b78db8727f541ab88e59f9c44f4c377.html</t>
-        </is>
-      </c>
-      <c r="I122" s="2" t="inlineStr"/>
-      <c r="J122" s="2" t="inlineStr">
-        <is>
-          <t>SAP S/4HANA Cloud Public Edition</t>
-        </is>
-      </c>
-      <c r="K122" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/2b5df257-bdfd-4396-a48b-a8362b2e02f7/</t>
-        </is>
-      </c>
-      <c r="L122" s="2" t="inlineStr"/>
-    </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
-        <is>
-          <t>Fixed Asset Key Figures Explanation</t>
-        </is>
-      </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>J966</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>AI Feature</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
-        <is>
-          <t>No existe enlace de Initial Setup en la sección Resources.</t>
-        </is>
-      </c>
-      <c r="E123" s="2" t="inlineStr">
-        <is>
-          <t>No existe enlace de Initial Setup en la sección Resources.</t>
-        </is>
-      </c>
-      <c r="F123" s="2" t="inlineStr">
-        <is>
-          <t>No existe enlace de Initial Setup en la sección Resources.</t>
-        </is>
-      </c>
-      <c r="G123" s="2" t="inlineStr">
-        <is>
-          <t>No evaluable: no existe enlace de Initial Setup en la sección Resources.</t>
-        </is>
-      </c>
-      <c r="H123" s="2" t="inlineStr"/>
-      <c r="I123" s="2" t="inlineStr"/>
-      <c r="J123" s="2" t="inlineStr"/>
-      <c r="K123" s="2" t="inlineStr"/>
-      <c r="L123" s="2" t="inlineStr"/>
-    </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
-        <is>
-          <t>Transformation Advisory‚ Initiative Builder</t>
-        </is>
-      </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>J967</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>No disponible</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
-        <is>
-          <t>No existe enlace de Initial Setup en la sección Resources</t>
-        </is>
-      </c>
-      <c r="E124" s="2" t="inlineStr">
-        <is>
-          <t>No existe enlace de Initial Setup en la sección Resources</t>
-        </is>
-      </c>
-      <c r="F124" s="2" t="inlineStr">
-        <is>
-          <t>No existe enlace de Initial Setup en la sección Resources</t>
-        </is>
-      </c>
-      <c r="G124" s="2" t="inlineStr">
-        <is>
-          <t>No aplica</t>
-        </is>
-      </c>
-      <c r="H124" s="2" t="inlineStr">
-        <is>
-          <t>No existe enlace de Initial Setup en la sección Resources</t>
-        </is>
-      </c>
-      <c r="I124" s="2" t="inlineStr"/>
-      <c r="J124" s="2" t="inlineStr">
-        <is>
-          <t>SAP Signavio solutions</t>
-        </is>
-      </c>
-      <c r="K124" s="2" t="inlineStr">
-        <is>
-          <t>https://discovery-center.cloud.sap/ai-feature/9ced0e83-412a-4e06-beda-6ef81e4bce95/</t>
-        </is>
-      </c>
-      <c r="L124" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
